--- a/app_unified/dist/PUMPS (1).xlsx
+++ b/app_unified/dist/PUMPS (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\OneDrive\Desktop\ESP DESING ESTUDIO\app_unified\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE71E1C4-371A-4A3E-948A-7EB0E44AD9FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E36F49-F0FA-450F-9DEB-2D8748DE0FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FC341EB1-65C7-47F8-9E2D-590F22EBE9EA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FC341EB1-65C7-47F8-9E2D-590F22EBE9EA}"/>
   </bookViews>
   <sheets>
     <sheet name="PUMP" sheetId="1" r:id="rId1"/>
@@ -312,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="535">
   <si>
     <t>Required Pump data</t>
   </si>
@@ -1737,9 +1737,6 @@
     <t>-1.86E-19</t>
   </si>
   <si>
-    <t>SLB</t>
-  </si>
-  <si>
     <t>S4000N</t>
   </si>
   <si>
@@ -1834,6 +1831,144 @@
   </si>
   <si>
     <t>0.875</t>
+  </si>
+  <si>
+    <t>Schlumberger</t>
+  </si>
+  <si>
+    <t>DN 1050</t>
+  </si>
+  <si>
+    <t>71.2</t>
+  </si>
+  <si>
+    <t>55.42</t>
+  </si>
+  <si>
+    <t>-0.01152</t>
+  </si>
+  <si>
+    <t>0.125</t>
+  </si>
+  <si>
+    <t>0.0001845</t>
+  </si>
+  <si>
+    <t>5.12e-15</t>
+  </si>
+  <si>
+    <t>4.00</t>
+  </si>
+  <si>
+    <t>0.688</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>DN 1400</t>
+  </si>
+  <si>
+    <t>72.5</t>
+  </si>
+  <si>
+    <t>48.65</t>
+  </si>
+  <si>
+    <t>-0.008542</t>
+  </si>
+  <si>
+    <t>4.85e-09</t>
+  </si>
+  <si>
+    <t>-8.24e-13</t>
+  </si>
+  <si>
+    <t>0.155</t>
+  </si>
+  <si>
+    <t>0.0002145</t>
+  </si>
+  <si>
+    <t>9.85e-08</t>
+  </si>
+  <si>
+    <t>-3.54e-11</t>
+  </si>
+  <si>
+    <t>73.8</t>
+  </si>
+  <si>
+    <t>42.15</t>
+  </si>
+  <si>
+    <t>-0.006425</t>
+  </si>
+  <si>
+    <t>-9.84e-06</t>
+  </si>
+  <si>
+    <t>3.12e-09</t>
+  </si>
+  <si>
+    <t>-5.45e-13</t>
+  </si>
+  <si>
+    <t>0.185</t>
+  </si>
+  <si>
+    <t>0.000245</t>
+  </si>
+  <si>
+    <t>8.12e-08</t>
+  </si>
+  <si>
+    <t>-2.85e-11</t>
+  </si>
+  <si>
+    <t>3.12e-15</t>
+  </si>
+  <si>
+    <t>DN 1750</t>
+  </si>
+  <si>
+    <t>DN 1800</t>
+  </si>
+  <si>
+    <t>74.2</t>
+  </si>
+  <si>
+    <t>41.5</t>
+  </si>
+  <si>
+    <t>-0.00585</t>
+  </si>
+  <si>
+    <t>-9.12e-06</t>
+  </si>
+  <si>
+    <t>2.85e-09</t>
+  </si>
+  <si>
+    <t>-4.95e-13</t>
+  </si>
+  <si>
+    <t>0.198</t>
+  </si>
+  <si>
+    <t>0.000258</t>
+  </si>
+  <si>
+    <t>7.45e-08</t>
+  </si>
+  <si>
+    <t>-2.42e-11</t>
+  </si>
+  <si>
+    <t>2.85e-15</t>
   </si>
 </sst>
 </file>
@@ -2802,7 +2937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{053E6D0B-9E01-4484-8758-0E93695A87D4}">
-  <dimension ref="A1:AJ1105"/>
+  <dimension ref="A1:AJ1104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="19.6640625" customWidth="1"/>
@@ -17876,14 +18011,14 @@
       </c>
     </row>
     <row r="153" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="14" t="s">
-        <v>457</v>
+      <c r="A153" s="68" t="s">
+        <v>489</v>
       </c>
       <c r="B153" s="93">
         <v>538</v>
       </c>
       <c r="C153" s="93" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D153" s="93">
         <v>1000</v>
@@ -17895,10 +18030,10 @@
         <v>6000</v>
       </c>
       <c r="G153" s="93" t="s">
+        <v>458</v>
+      </c>
+      <c r="H153" s="93" t="s">
         <v>459</v>
-      </c>
-      <c r="H153" s="93" t="s">
-        <v>460</v>
       </c>
       <c r="I153" s="93">
         <v>7500</v>
@@ -17907,43 +18042,43 @@
         <v>60</v>
       </c>
       <c r="K153" s="78" t="s">
+        <v>460</v>
+      </c>
+      <c r="L153" s="78" t="s">
         <v>461</v>
       </c>
-      <c r="L153" s="78" t="s">
+      <c r="M153" s="78" t="s">
         <v>462</v>
       </c>
-      <c r="M153" s="78" t="s">
+      <c r="N153" s="78" t="s">
         <v>463</v>
       </c>
-      <c r="N153" s="78" t="s">
+      <c r="O153" s="78" t="s">
         <v>464</v>
       </c>
-      <c r="O153" s="78" t="s">
+      <c r="P153" s="78" t="s">
         <v>465</v>
       </c>
-      <c r="P153" s="78" t="s">
+      <c r="Q153" s="78" t="s">
         <v>466</v>
       </c>
-      <c r="Q153" s="78" t="s">
+      <c r="R153" s="78" t="s">
         <v>467</v>
       </c>
-      <c r="R153" s="78" t="s">
+      <c r="S153" s="78" t="s">
         <v>468</v>
       </c>
-      <c r="S153" s="78" t="s">
+      <c r="T153" s="78" t="s">
         <v>469</v>
       </c>
-      <c r="T153" s="78" t="s">
+      <c r="U153" s="78" t="s">
         <v>470</v>
       </c>
-      <c r="U153" s="78" t="s">
+      <c r="V153" s="78" t="s">
         <v>471</v>
       </c>
-      <c r="V153" s="78" t="s">
+      <c r="W153" s="80" t="s">
         <v>472</v>
-      </c>
-      <c r="W153" s="80" t="s">
-        <v>473</v>
       </c>
       <c r="X153" s="100" t="s">
         <v>440</v>
@@ -17981,7 +18116,7 @@
         <v>538</v>
       </c>
       <c r="C154" s="93" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D154" s="93">
         <v>200</v>
@@ -17993,10 +18128,10 @@
         <v>2250</v>
       </c>
       <c r="G154" s="93" t="s">
+        <v>474</v>
+      </c>
+      <c r="H154" s="93" t="s">
         <v>475</v>
-      </c>
-      <c r="H154" s="93" t="s">
-        <v>476</v>
       </c>
       <c r="I154" s="93">
         <v>3000</v>
@@ -18005,43 +18140,43 @@
         <v>60</v>
       </c>
       <c r="K154" s="78" t="s">
+        <v>476</v>
+      </c>
+      <c r="L154" s="78" t="s">
         <v>477</v>
       </c>
-      <c r="L154" s="78" t="s">
+      <c r="M154" s="78" t="s">
         <v>478</v>
       </c>
-      <c r="M154" s="78" t="s">
+      <c r="N154" s="78" t="s">
         <v>479</v>
       </c>
-      <c r="N154" s="78" t="s">
+      <c r="O154" s="78" t="s">
         <v>480</v>
       </c>
-      <c r="O154" s="78" t="s">
+      <c r="P154" s="78" t="s">
         <v>481</v>
       </c>
-      <c r="P154" s="78" t="s">
+      <c r="Q154" s="78" t="s">
         <v>482</v>
       </c>
-      <c r="Q154" s="78" t="s">
+      <c r="R154" s="78" t="s">
         <v>483</v>
       </c>
-      <c r="R154" s="78" t="s">
+      <c r="S154" s="78" t="s">
         <v>484</v>
       </c>
-      <c r="S154" s="78" t="s">
+      <c r="T154" s="78" t="s">
         <v>485</v>
       </c>
-      <c r="T154" s="78" t="s">
+      <c r="U154" s="78" t="s">
         <v>486</v>
       </c>
-      <c r="U154" s="78" t="s">
+      <c r="V154" s="78" t="s">
         <v>487</v>
       </c>
-      <c r="V154" s="78" t="s">
-        <v>488</v>
-      </c>
       <c r="W154" s="80" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="X154" s="100">
         <v>5627</v>
@@ -18050,7 +18185,7 @@
         <v>440</v>
       </c>
       <c r="Z154" s="82" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AA154" s="100" t="s">
         <v>440</v>
@@ -18072,140 +18207,420 @@
       </c>
     </row>
     <row r="155" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="68"/>
-      <c r="B155" s="93"/>
-      <c r="C155" s="93"/>
-      <c r="D155" s="93"/>
-      <c r="E155" s="93"/>
-      <c r="F155" s="93"/>
-      <c r="G155" s="93"/>
-      <c r="H155" s="93"/>
-      <c r="I155" s="93"/>
-      <c r="J155" s="72"/>
-      <c r="K155" s="78"/>
-      <c r="L155" s="78"/>
-      <c r="M155" s="78"/>
-      <c r="N155" s="78"/>
-      <c r="O155" s="78"/>
-      <c r="P155" s="78"/>
-      <c r="Q155" s="78"/>
-      <c r="R155" s="78"/>
-      <c r="S155" s="78"/>
-      <c r="T155" s="78"/>
-      <c r="U155" s="78"/>
-      <c r="V155" s="78"/>
-      <c r="W155" s="80"/>
-      <c r="X155" s="100"/>
-      <c r="Y155" s="100"/>
-      <c r="Z155" s="82"/>
-      <c r="AA155" s="100"/>
-      <c r="AB155" s="100"/>
-      <c r="AC155" s="101"/>
-      <c r="AD155" s="101"/>
-      <c r="AE155" s="101"/>
-      <c r="AF155" s="98"/>
+      <c r="A155" s="68" t="s">
+        <v>489</v>
+      </c>
+      <c r="B155" s="93">
+        <v>400</v>
+      </c>
+      <c r="C155" s="93" t="s">
+        <v>490</v>
+      </c>
+      <c r="D155" s="93">
+        <v>300</v>
+      </c>
+      <c r="E155" s="93">
+        <v>1050</v>
+      </c>
+      <c r="F155" s="93">
+        <v>1650</v>
+      </c>
+      <c r="G155" s="93" t="s">
+        <v>491</v>
+      </c>
+      <c r="H155" s="93" t="s">
+        <v>492</v>
+      </c>
+      <c r="I155" s="93">
+        <v>1800</v>
+      </c>
+      <c r="J155" s="72" t="s">
+        <v>492</v>
+      </c>
+      <c r="K155" s="78" t="s">
+        <v>493</v>
+      </c>
+      <c r="L155" s="78">
+        <v>-1.54E-2</v>
+      </c>
+      <c r="M155" s="78">
+        <v>6.2099999999999998E-6</v>
+      </c>
+      <c r="N155" s="78">
+        <v>-1.03E-9</v>
+      </c>
+      <c r="O155" s="78">
+        <v>0</v>
+      </c>
+      <c r="P155" s="78" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q155" s="78" t="s">
+        <v>495</v>
+      </c>
+      <c r="R155" s="78">
+        <v>1.12E-4</v>
+      </c>
+      <c r="S155" s="78">
+        <v>-4.1299999999999999E-8</v>
+      </c>
+      <c r="T155" s="78" t="s">
+        <v>496</v>
+      </c>
+      <c r="U155" s="78">
+        <v>0</v>
+      </c>
+      <c r="V155" s="78" t="s">
+        <v>497</v>
+      </c>
+      <c r="W155" s="80">
+        <v>5000</v>
+      </c>
+      <c r="X155" s="100">
+        <v>6000</v>
+      </c>
+      <c r="Y155" s="100" t="s">
+        <v>498</v>
+      </c>
+      <c r="Z155" s="82">
+        <v>154</v>
+      </c>
+      <c r="AA155" s="100">
+        <v>240</v>
+      </c>
+      <c r="AB155" s="100">
+        <v>1</v>
+      </c>
+      <c r="AC155" s="101">
+        <v>400</v>
+      </c>
+      <c r="AD155" s="101">
+        <v>1</v>
+      </c>
+      <c r="AE155" s="101">
+        <v>105</v>
+      </c>
+      <c r="AF155" s="98" t="s">
+        <v>499</v>
+      </c>
+      <c r="AG155" s="44">
+        <v>1050</v>
+      </c>
+      <c r="AH155" s="44" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="156" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="68"/>
-      <c r="B156" s="93"/>
-      <c r="C156" s="93"/>
-      <c r="D156" s="93"/>
-      <c r="E156" s="93"/>
-      <c r="F156" s="93"/>
-      <c r="G156" s="93"/>
-      <c r="H156" s="93"/>
-      <c r="I156" s="93"/>
-      <c r="J156" s="72"/>
-      <c r="K156" s="78"/>
-      <c r="L156" s="78"/>
-      <c r="M156" s="78"/>
-      <c r="N156" s="78"/>
-      <c r="O156" s="78"/>
-      <c r="P156" s="78"/>
-      <c r="Q156" s="78"/>
-      <c r="R156" s="78"/>
-      <c r="S156" s="78"/>
-      <c r="T156" s="78"/>
-      <c r="U156" s="78"/>
-      <c r="V156" s="78"/>
-      <c r="W156" s="80"/>
-      <c r="X156" s="100"/>
-      <c r="Y156" s="100"/>
-      <c r="Z156" s="82"/>
-      <c r="AA156" s="100"/>
-      <c r="AB156" s="100"/>
-      <c r="AC156" s="101"/>
-      <c r="AD156" s="101"/>
-      <c r="AE156" s="101"/>
-      <c r="AF156" s="98"/>
+      <c r="A156" s="68" t="s">
+        <v>489</v>
+      </c>
+      <c r="B156" s="93">
+        <v>400</v>
+      </c>
+      <c r="C156" s="93" t="s">
+        <v>501</v>
+      </c>
+      <c r="D156" s="93">
+        <v>400</v>
+      </c>
+      <c r="E156" s="93">
+        <v>1400</v>
+      </c>
+      <c r="F156" s="93">
+        <v>2200</v>
+      </c>
+      <c r="G156" s="93" t="s">
+        <v>502</v>
+      </c>
+      <c r="H156" s="93" t="s">
+        <v>503</v>
+      </c>
+      <c r="I156" s="93">
+        <v>2500</v>
+      </c>
+      <c r="J156" s="72" t="s">
+        <v>503</v>
+      </c>
+      <c r="K156" s="78" t="s">
+        <v>504</v>
+      </c>
+      <c r="L156" s="78">
+        <v>-1.1299999999999999E-2</v>
+      </c>
+      <c r="M156" s="78" t="s">
+        <v>505</v>
+      </c>
+      <c r="N156" s="78" t="s">
+        <v>506</v>
+      </c>
+      <c r="O156" s="78">
+        <v>0</v>
+      </c>
+      <c r="P156" s="78" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q156" s="78" t="s">
+        <v>508</v>
+      </c>
+      <c r="R156" s="78" t="s">
+        <v>509</v>
+      </c>
+      <c r="S156" s="78" t="s">
+        <v>510</v>
+      </c>
+      <c r="T156" s="78">
+        <v>4.2200000000000002E-12</v>
+      </c>
+      <c r="U156" s="78">
+        <v>0</v>
+      </c>
+      <c r="V156" s="78" t="s">
+        <v>497</v>
+      </c>
+      <c r="W156" s="80">
+        <v>5000</v>
+      </c>
+      <c r="X156" s="100">
+        <v>6000</v>
+      </c>
+      <c r="Y156" s="100" t="s">
+        <v>498</v>
+      </c>
+      <c r="Z156" s="82">
+        <v>154</v>
+      </c>
+      <c r="AA156" s="100">
+        <v>240</v>
+      </c>
+      <c r="AB156" s="100">
+        <v>1</v>
+      </c>
+      <c r="AC156" s="101">
+        <v>400</v>
+      </c>
+      <c r="AD156" s="101">
+        <v>1</v>
+      </c>
+      <c r="AE156" s="101">
+        <v>163</v>
+      </c>
+      <c r="AF156" s="98" t="s">
+        <v>499</v>
+      </c>
+      <c r="AG156" s="44">
+        <v>1400</v>
+      </c>
+      <c r="AH156" s="44" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="157" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="68"/>
-      <c r="B157" s="93"/>
-      <c r="C157" s="93"/>
-      <c r="D157" s="93"/>
-      <c r="E157" s="93"/>
-      <c r="F157" s="93"/>
-      <c r="G157" s="93"/>
-      <c r="H157" s="93"/>
-      <c r="I157" s="93"/>
-      <c r="J157" s="72"/>
-      <c r="K157" s="78"/>
-      <c r="L157" s="78"/>
-      <c r="M157" s="78"/>
-      <c r="N157" s="78"/>
-      <c r="O157" s="78"/>
-      <c r="P157" s="78"/>
-      <c r="Q157" s="78"/>
-      <c r="R157" s="78"/>
-      <c r="S157" s="78"/>
-      <c r="T157" s="78"/>
-      <c r="U157" s="78"/>
-      <c r="V157" s="78"/>
-      <c r="W157" s="80"/>
-      <c r="X157" s="100"/>
-      <c r="Y157" s="100"/>
-      <c r="Z157" s="82"/>
-      <c r="AA157" s="100"/>
-      <c r="AB157" s="100"/>
-      <c r="AC157" s="101"/>
-      <c r="AD157" s="101"/>
-      <c r="AE157" s="101"/>
-      <c r="AF157" s="98"/>
+      <c r="A157" s="68" t="s">
+        <v>489</v>
+      </c>
+      <c r="B157" s="93">
+        <v>400</v>
+      </c>
+      <c r="C157" s="93" t="s">
+        <v>522</v>
+      </c>
+      <c r="D157" s="93">
+        <v>500</v>
+      </c>
+      <c r="E157" s="93">
+        <v>1750</v>
+      </c>
+      <c r="F157" s="93">
+        <v>2700</v>
+      </c>
+      <c r="G157" s="93" t="s">
+        <v>511</v>
+      </c>
+      <c r="H157" s="93" t="s">
+        <v>512</v>
+      </c>
+      <c r="I157" s="93">
+        <v>3000</v>
+      </c>
+      <c r="J157" s="72" t="s">
+        <v>512</v>
+      </c>
+      <c r="K157" s="78" t="s">
+        <v>513</v>
+      </c>
+      <c r="L157" s="78" t="s">
+        <v>514</v>
+      </c>
+      <c r="M157" s="78" t="s">
+        <v>515</v>
+      </c>
+      <c r="N157" s="78" t="s">
+        <v>516</v>
+      </c>
+      <c r="O157" s="78">
+        <v>0</v>
+      </c>
+      <c r="P157" s="78" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q157" s="78" t="s">
+        <v>518</v>
+      </c>
+      <c r="R157" s="78" t="s">
+        <v>519</v>
+      </c>
+      <c r="S157" s="78" t="s">
+        <v>520</v>
+      </c>
+      <c r="T157" s="78" t="s">
+        <v>521</v>
+      </c>
+      <c r="U157" s="78">
+        <v>0</v>
+      </c>
+      <c r="V157" s="78" t="s">
+        <v>497</v>
+      </c>
+      <c r="W157" s="80">
+        <v>5000</v>
+      </c>
+      <c r="X157" s="100">
+        <v>6000</v>
+      </c>
+      <c r="Y157" s="100" t="s">
+        <v>498</v>
+      </c>
+      <c r="Z157" s="82">
+        <v>154</v>
+      </c>
+      <c r="AA157" s="100">
+        <v>240</v>
+      </c>
+      <c r="AB157" s="100">
+        <v>1</v>
+      </c>
+      <c r="AC157" s="101">
+        <v>400</v>
+      </c>
+      <c r="AD157" s="101">
+        <v>1</v>
+      </c>
+      <c r="AE157" s="101">
+        <v>93</v>
+      </c>
+      <c r="AF157" s="98" t="s">
+        <v>499</v>
+      </c>
+      <c r="AG157" s="44">
+        <v>1750</v>
+      </c>
+      <c r="AH157" s="44" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="158" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="68"/>
-      <c r="B158" s="93"/>
-      <c r="C158" s="93"/>
-      <c r="D158" s="93"/>
-      <c r="E158" s="93"/>
-      <c r="F158" s="93"/>
-      <c r="G158" s="93"/>
-      <c r="H158" s="93"/>
-      <c r="I158" s="93"/>
-      <c r="J158" s="72"/>
-      <c r="K158" s="78"/>
-      <c r="L158" s="78"/>
-      <c r="M158" s="78"/>
-      <c r="N158" s="78"/>
-      <c r="O158" s="78"/>
-      <c r="P158" s="78"/>
-      <c r="Q158" s="78"/>
-      <c r="R158" s="78"/>
-      <c r="S158" s="78"/>
-      <c r="T158" s="78"/>
-      <c r="U158" s="78"/>
-      <c r="V158" s="78"/>
-      <c r="W158" s="80"/>
-      <c r="X158" s="100"/>
-      <c r="Y158" s="100"/>
-      <c r="Z158" s="82"/>
-      <c r="AA158" s="100"/>
-      <c r="AB158" s="100"/>
-      <c r="AC158" s="101"/>
-      <c r="AD158" s="101"/>
-      <c r="AE158" s="101"/>
-      <c r="AF158" s="98"/>
+      <c r="A158" s="68" t="s">
+        <v>489</v>
+      </c>
+      <c r="B158" s="93">
+        <v>400</v>
+      </c>
+      <c r="C158" s="93" t="s">
+        <v>523</v>
+      </c>
+      <c r="D158" s="93">
+        <v>600</v>
+      </c>
+      <c r="E158" s="93">
+        <v>1800</v>
+      </c>
+      <c r="F158" s="93">
+        <v>2850</v>
+      </c>
+      <c r="G158" s="93" t="s">
+        <v>524</v>
+      </c>
+      <c r="H158" s="93" t="s">
+        <v>525</v>
+      </c>
+      <c r="I158" s="93">
+        <v>3200</v>
+      </c>
+      <c r="J158" s="72" t="s">
+        <v>525</v>
+      </c>
+      <c r="K158" s="78" t="s">
+        <v>526</v>
+      </c>
+      <c r="L158" s="78" t="s">
+        <v>527</v>
+      </c>
+      <c r="M158" s="78" t="s">
+        <v>528</v>
+      </c>
+      <c r="N158" s="78" t="s">
+        <v>529</v>
+      </c>
+      <c r="O158" s="78">
+        <v>0</v>
+      </c>
+      <c r="P158" s="78" t="s">
+        <v>530</v>
+      </c>
+      <c r="Q158" s="78" t="s">
+        <v>531</v>
+      </c>
+      <c r="R158" s="78" t="s">
+        <v>532</v>
+      </c>
+      <c r="S158" s="78" t="s">
+        <v>533</v>
+      </c>
+      <c r="T158" s="78" t="s">
+        <v>534</v>
+      </c>
+      <c r="U158" s="78">
+        <v>0</v>
+      </c>
+      <c r="V158" s="78" t="s">
+        <v>497</v>
+      </c>
+      <c r="W158" s="80">
+        <v>5000</v>
+      </c>
+      <c r="X158" s="100">
+        <v>6000</v>
+      </c>
+      <c r="Y158" s="100" t="s">
+        <v>498</v>
+      </c>
+      <c r="Z158" s="82">
+        <v>154</v>
+      </c>
+      <c r="AA158" s="100">
+        <v>240</v>
+      </c>
+      <c r="AB158" s="100">
+        <v>1</v>
+      </c>
+      <c r="AC158" s="101">
+        <v>400</v>
+      </c>
+      <c r="AD158" s="101">
+        <v>1</v>
+      </c>
+      <c r="AE158" s="101">
+        <v>117</v>
+      </c>
+      <c r="AF158" s="98" t="s">
+        <v>499</v>
+      </c>
+      <c r="AG158" s="44">
+        <v>1800</v>
+      </c>
+      <c r="AH158" s="44" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="159" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="32"/>
@@ -18253,6 +18668,7 @@
       <c r="N160" s="24"/>
       <c r="O160" s="24"/>
       <c r="P160" s="24"/>
+      <c r="Q160" s="24"/>
       <c r="R160" s="24"/>
       <c r="S160" s="24"/>
       <c r="T160" s="24"/>
@@ -18279,6 +18695,7 @@
       <c r="G161" s="27"/>
       <c r="H161" s="27"/>
       <c r="J161" s="24"/>
+      <c r="K161" s="24"/>
       <c r="L161" s="24"/>
       <c r="M161" s="24"/>
       <c r="N161" s="24"/>
@@ -18310,7 +18727,8 @@
       <c r="F162" s="27"/>
       <c r="G162" s="27"/>
       <c r="H162" s="27"/>
-      <c r="J162" s="24"/>
+      <c r="I162" s="24"/>
+      <c r="J162" s="27"/>
       <c r="K162" s="24"/>
       <c r="L162" s="24"/>
       <c r="M162" s="24"/>
@@ -18343,7 +18761,7 @@
       <c r="F163" s="27"/>
       <c r="G163" s="27"/>
       <c r="H163" s="27"/>
-      <c r="I163" s="24"/>
+      <c r="I163" s="27"/>
       <c r="J163" s="27"/>
       <c r="K163" s="24"/>
       <c r="L163" s="24"/>
@@ -18604,7 +19022,9 @@
       <c r="AC170" s="31"/>
       <c r="AD170" s="31"/>
       <c r="AE170" s="31"/>
-      <c r="AF170" s="36"/>
+      <c r="AF170" s="37"/>
+      <c r="AG170" s="45"/>
+      <c r="AH170" s="45"/>
     </row>
     <row r="171" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="32"/>
@@ -18638,9 +19058,7 @@
       <c r="AC171" s="31"/>
       <c r="AD171" s="31"/>
       <c r="AE171" s="31"/>
-      <c r="AF171" s="37"/>
-      <c r="AG171" s="45"/>
-      <c r="AH171" s="45"/>
+      <c r="AF171" s="36"/>
     </row>
     <row r="172" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="32"/>
@@ -18744,7 +19162,7 @@
       <c r="AE174" s="31"/>
       <c r="AF174" s="36"/>
     </row>
-    <row r="175" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:34" s="46" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="32"/>
       <c r="B175" s="27"/>
       <c r="C175" s="33"/>
@@ -18776,9 +19194,9 @@
       <c r="AC175" s="31"/>
       <c r="AD175" s="31"/>
       <c r="AE175" s="31"/>
-      <c r="AF175" s="36"/>
-    </row>
-    <row r="176" spans="1:34" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AF175" s="38"/>
+    </row>
+    <row r="176" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="32"/>
       <c r="B176" s="27"/>
       <c r="C176" s="33"/>
@@ -18811,8 +19229,10 @@
       <c r="AD176" s="31"/>
       <c r="AE176" s="31"/>
       <c r="AF176" s="38"/>
-    </row>
-    <row r="177" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AG176" s="46"/>
+      <c r="AH176" s="46"/>
+    </row>
+    <row r="177" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="32"/>
       <c r="B177" s="27"/>
       <c r="C177" s="33"/>
@@ -18844,11 +19264,9 @@
       <c r="AC177" s="31"/>
       <c r="AD177" s="31"/>
       <c r="AE177" s="31"/>
-      <c r="AF177" s="38"/>
-      <c r="AG177" s="46"/>
-      <c r="AH177" s="46"/>
-    </row>
-    <row r="178" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AF177" s="36"/>
+    </row>
+    <row r="178" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="32"/>
       <c r="B178" s="27"/>
       <c r="C178" s="33"/>
@@ -18882,41 +19300,42 @@
       <c r="AE178" s="31"/>
       <c r="AF178" s="36"/>
     </row>
-    <row r="179" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="32"/>
-      <c r="B179" s="27"/>
-      <c r="C179" s="33"/>
-      <c r="D179" s="27"/>
-      <c r="E179" s="27"/>
-      <c r="F179" s="27"/>
-      <c r="G179" s="27"/>
-      <c r="H179" s="27"/>
-      <c r="I179" s="27"/>
-      <c r="J179" s="27"/>
-      <c r="K179" s="24"/>
-      <c r="L179" s="24"/>
-      <c r="M179" s="24"/>
-      <c r="N179" s="24"/>
-      <c r="O179" s="24"/>
-      <c r="P179" s="24"/>
-      <c r="Q179" s="24"/>
-      <c r="R179" s="24"/>
-      <c r="S179" s="24"/>
-      <c r="T179" s="24"/>
-      <c r="U179" s="24"/>
-      <c r="V179" s="24"/>
-      <c r="W179" s="29"/>
-      <c r="X179" s="30"/>
-      <c r="Y179" s="30"/>
-      <c r="Z179" s="26"/>
-      <c r="AA179" s="30"/>
-      <c r="AB179" s="30"/>
-      <c r="AC179" s="31"/>
-      <c r="AD179" s="31"/>
-      <c r="AE179" s="31"/>
-      <c r="AF179" s="36"/>
-    </row>
-    <row r="180" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="35"/>
+      <c r="B179" s="23"/>
+      <c r="C179" s="40"/>
+      <c r="D179" s="40"/>
+      <c r="E179" s="41"/>
+      <c r="F179" s="41"/>
+      <c r="G179" s="41"/>
+      <c r="H179" s="42"/>
+      <c r="I179" s="42"/>
+      <c r="J179" s="42"/>
+      <c r="K179" s="43"/>
+      <c r="L179" s="43"/>
+      <c r="M179" s="43"/>
+      <c r="N179" s="43"/>
+      <c r="O179" s="43"/>
+      <c r="P179" s="43"/>
+      <c r="Q179" s="43"/>
+      <c r="R179" s="43"/>
+      <c r="S179" s="43"/>
+      <c r="T179" s="43"/>
+      <c r="U179" s="43"/>
+      <c r="V179" s="43"/>
+      <c r="W179" s="42"/>
+      <c r="X179" s="42"/>
+      <c r="Y179" s="42"/>
+      <c r="Z179" s="42"/>
+      <c r="AA179" s="42"/>
+      <c r="AB179" s="42"/>
+      <c r="AC179" s="36"/>
+      <c r="AD179" s="36"/>
+      <c r="AE179" s="36"/>
+      <c r="AF179" s="42"/>
+      <c r="AG179" s="36"/>
+    </row>
+    <row r="180" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A180" s="35"/>
       <c r="B180" s="23"/>
       <c r="C180" s="40"/>
@@ -18951,7 +19370,7 @@
       <c r="AF180" s="42"/>
       <c r="AG180" s="36"/>
     </row>
-    <row r="181" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A181" s="35"/>
       <c r="B181" s="23"/>
       <c r="C181" s="40"/>
@@ -18986,7 +19405,7 @@
       <c r="AF181" s="42"/>
       <c r="AG181" s="36"/>
     </row>
-    <row r="182" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A182" s="35"/>
       <c r="B182" s="23"/>
       <c r="C182" s="40"/>
@@ -19021,7 +19440,7 @@
       <c r="AF182" s="42"/>
       <c r="AG182" s="36"/>
     </row>
-    <row r="183" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A183" s="35"/>
       <c r="B183" s="23"/>
       <c r="C183" s="40"/>
@@ -19056,7 +19475,7 @@
       <c r="AF183" s="42"/>
       <c r="AG183" s="36"/>
     </row>
-    <row r="184" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A184" s="35"/>
       <c r="B184" s="23"/>
       <c r="C184" s="40"/>
@@ -19091,7 +19510,7 @@
       <c r="AF184" s="42"/>
       <c r="AG184" s="36"/>
     </row>
-    <row r="185" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A185" s="35"/>
       <c r="B185" s="23"/>
       <c r="C185" s="40"/>
@@ -19126,7 +19545,7 @@
       <c r="AF185" s="42"/>
       <c r="AG185" s="36"/>
     </row>
-    <row r="186" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A186" s="35"/>
       <c r="B186" s="23"/>
       <c r="C186" s="40"/>
@@ -19161,7 +19580,7 @@
       <c r="AF186" s="42"/>
       <c r="AG186" s="36"/>
     </row>
-    <row r="187" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A187" s="35"/>
       <c r="B187" s="23"/>
       <c r="C187" s="40"/>
@@ -19196,7 +19615,7 @@
       <c r="AF187" s="42"/>
       <c r="AG187" s="36"/>
     </row>
-    <row r="188" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A188" s="35"/>
       <c r="B188" s="23"/>
       <c r="C188" s="40"/>
@@ -19231,7 +19650,7 @@
       <c r="AF188" s="42"/>
       <c r="AG188" s="36"/>
     </row>
-    <row r="189" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A189" s="35"/>
       <c r="B189" s="23"/>
       <c r="C189" s="40"/>
@@ -19266,7 +19685,7 @@
       <c r="AF189" s="42"/>
       <c r="AG189" s="36"/>
     </row>
-    <row r="190" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A190" s="35"/>
       <c r="B190" s="23"/>
       <c r="C190" s="40"/>
@@ -19301,7 +19720,7 @@
       <c r="AF190" s="42"/>
       <c r="AG190" s="36"/>
     </row>
-    <row r="191" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A191" s="35"/>
       <c r="B191" s="23"/>
       <c r="C191" s="40"/>
@@ -19336,7 +19755,7 @@
       <c r="AF191" s="42"/>
       <c r="AG191" s="36"/>
     </row>
-    <row r="192" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A192" s="35"/>
       <c r="B192" s="23"/>
       <c r="C192" s="40"/>
@@ -19792,7 +20211,7 @@
       <c r="AG204" s="36"/>
     </row>
     <row r="205" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="35"/>
+      <c r="A205" s="39"/>
       <c r="B205" s="23"/>
       <c r="C205" s="40"/>
       <c r="D205" s="40"/>
@@ -24202,7 +24621,6 @@
       <c r="AG330" s="36"/>
     </row>
     <row r="331" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A331" s="39"/>
       <c r="B331" s="23"/>
       <c r="C331" s="40"/>
       <c r="D331" s="40"/>
@@ -49974,7 +50392,7 @@
       <c r="AF1088" s="42"/>
       <c r="AG1088" s="36"/>
     </row>
-    <row r="1089" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1089" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1089" s="23"/>
       <c r="C1089" s="40"/>
       <c r="D1089" s="40"/>
@@ -50008,7 +50426,7 @@
       <c r="AF1089" s="42"/>
       <c r="AG1089" s="36"/>
     </row>
-    <row r="1090" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1090" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1090" s="23"/>
       <c r="C1090" s="40"/>
       <c r="D1090" s="40"/>
@@ -50042,7 +50460,7 @@
       <c r="AF1090" s="42"/>
       <c r="AG1090" s="36"/>
     </row>
-    <row r="1091" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1091" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1091" s="23"/>
       <c r="C1091" s="40"/>
       <c r="D1091" s="40"/>
@@ -50076,7 +50494,7 @@
       <c r="AF1091" s="42"/>
       <c r="AG1091" s="36"/>
     </row>
-    <row r="1092" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1092" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1092" s="23"/>
       <c r="C1092" s="40"/>
       <c r="D1092" s="40"/>
@@ -50110,7 +50528,7 @@
       <c r="AF1092" s="42"/>
       <c r="AG1092" s="36"/>
     </row>
-    <row r="1093" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1093" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1093" s="23"/>
       <c r="C1093" s="40"/>
       <c r="D1093" s="40"/>
@@ -50144,7 +50562,7 @@
       <c r="AF1093" s="42"/>
       <c r="AG1093" s="36"/>
     </row>
-    <row r="1094" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1094" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1094" s="23"/>
       <c r="C1094" s="40"/>
       <c r="D1094" s="40"/>
@@ -50178,7 +50596,7 @@
       <c r="AF1094" s="42"/>
       <c r="AG1094" s="36"/>
     </row>
-    <row r="1095" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1095" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1095" s="23"/>
       <c r="C1095" s="40"/>
       <c r="D1095" s="40"/>
@@ -50212,7 +50630,7 @@
       <c r="AF1095" s="42"/>
       <c r="AG1095" s="36"/>
     </row>
-    <row r="1096" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1096" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1096" s="23"/>
       <c r="C1096" s="40"/>
       <c r="D1096" s="40"/>
@@ -50246,7 +50664,7 @@
       <c r="AF1096" s="42"/>
       <c r="AG1096" s="36"/>
     </row>
-    <row r="1097" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1097" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1097" s="23"/>
       <c r="C1097" s="40"/>
       <c r="D1097" s="40"/>
@@ -50280,7 +50698,7 @@
       <c r="AF1097" s="42"/>
       <c r="AG1097" s="36"/>
     </row>
-    <row r="1098" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1098" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1098" s="23"/>
       <c r="C1098" s="40"/>
       <c r="D1098" s="40"/>
@@ -50314,7 +50732,7 @@
       <c r="AF1098" s="42"/>
       <c r="AG1098" s="36"/>
     </row>
-    <row r="1099" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1099" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1099" s="23"/>
       <c r="C1099" s="40"/>
       <c r="D1099" s="40"/>
@@ -50348,7 +50766,7 @@
       <c r="AF1099" s="42"/>
       <c r="AG1099" s="36"/>
     </row>
-    <row r="1100" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1100" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1100" s="23"/>
       <c r="C1100" s="40"/>
       <c r="D1100" s="40"/>
@@ -50382,7 +50800,7 @@
       <c r="AF1100" s="42"/>
       <c r="AG1100" s="36"/>
     </row>
-    <row r="1101" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1101" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1101" s="23"/>
       <c r="C1101" s="40"/>
       <c r="D1101" s="40"/>
@@ -50416,7 +50834,7 @@
       <c r="AF1101" s="42"/>
       <c r="AG1101" s="36"/>
     </row>
-    <row r="1102" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1102" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1102" s="23"/>
       <c r="C1102" s="40"/>
       <c r="D1102" s="40"/>
@@ -50450,7 +50868,7 @@
       <c r="AF1102" s="42"/>
       <c r="AG1102" s="36"/>
     </row>
-    <row r="1103" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1103" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1103" s="23"/>
       <c r="C1103" s="40"/>
       <c r="D1103" s="40"/>
@@ -50484,8 +50902,9 @@
       <c r="AF1103" s="42"/>
       <c r="AG1103" s="36"/>
     </row>
-    <row r="1104" spans="2:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B1104" s="23"/>
+    <row r="1104" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1104" s="34"/>
+      <c r="B1104" s="40"/>
       <c r="C1104" s="40"/>
       <c r="D1104" s="40"/>
       <c r="E1104" s="41"/>
@@ -50518,53 +50937,18 @@
       <c r="AF1104" s="42"/>
       <c r="AG1104" s="36"/>
     </row>
-    <row r="1105" spans="1:33" s="44" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1105" s="34"/>
-      <c r="B1105" s="40"/>
-      <c r="C1105" s="40"/>
-      <c r="D1105" s="40"/>
-      <c r="E1105" s="41"/>
-      <c r="F1105" s="41"/>
-      <c r="G1105" s="41"/>
-      <c r="H1105" s="42"/>
-      <c r="I1105" s="42"/>
-      <c r="J1105" s="42"/>
-      <c r="K1105" s="43"/>
-      <c r="L1105" s="43"/>
-      <c r="M1105" s="43"/>
-      <c r="N1105" s="43"/>
-      <c r="O1105" s="43"/>
-      <c r="P1105" s="43"/>
-      <c r="Q1105" s="43"/>
-      <c r="R1105" s="43"/>
-      <c r="S1105" s="43"/>
-      <c r="T1105" s="43"/>
-      <c r="U1105" s="43"/>
-      <c r="V1105" s="43"/>
-      <c r="W1105" s="42"/>
-      <c r="X1105" s="42"/>
-      <c r="Y1105" s="42"/>
-      <c r="Z1105" s="42"/>
-      <c r="AA1105" s="42"/>
-      <c r="AB1105" s="42"/>
-      <c r="AC1105" s="36"/>
-      <c r="AD1105" s="36"/>
-      <c r="AE1105" s="36"/>
-      <c r="AF1105" s="42"/>
-      <c r="AG1105" s="36"/>
-    </row>
   </sheetData>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter 1 for gas handler" sqref="AH5:AH117" xr:uid="{D4F63CA9-4B8A-4E8D-8A06-46E288212DB9}">
-      <formula1>$A$1001:$A$1002</formula1>
+      <formula1>$A$1000:$A$1001</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter 1 for obsolete" sqref="AG5:AG117 AG180:AG1104 AF118:AF149 AF152:AF179" xr:uid="{6AE47EA0-4762-42E9-B62C-07E716141A03}">
-      <formula1>$A$1001:$A$1002</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter 1 for obsolete" sqref="AG5:AG117 AF152:AF178 AF118:AF149 AG179:AG1103" xr:uid="{6AE47EA0-4762-42E9-B62C-07E716141A03}">
+      <formula1>$A$1000:$A$1001</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Important Notice:" prompt="If a manufacturer is not the SubPUMP databank, this field is required. The available manufacturers within SubPUMP can be found in the drop down list in the manufacturer field (Column B)." sqref="W39 W82:W97 W7:W34 W42:W77 W79:W80 W99:W100 W103:W117" xr:uid="{3ABA8888-4F6D-4392-92AF-AB8BE0A86DDD}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Important Notice:" prompt="-------_x000a_If a manufacturer is not in SubPUMP databank, this field is required._x000a_-------_x000a_Manufacturers in SubPUMP:_x000a_Almaz, Alnas, Borets, CAI, Centrilift/ODI or CLift, ESP, Lemaz, Novomet, Novo, ODI, Schlumberger/Reda or Reda, Weatherford or Wford, WSP" sqref="W180:W1104 V176:V179 V118:V149 V162:V174 V152:V160" xr:uid="{9A547A56-E420-4C2C-BE7C-866904004891}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Manufacturer Name" prompt="Select a manufacturer from the list, or enter a new manufacturer using a short name" sqref="B180:B1104 A152:A179" xr:uid="{730E29A7-E193-4760-8A9E-D7881A70E46B}">
-      <formula1>$A$1010:$A$1022</formula1>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Important Notice:" prompt="-------_x000a_If a manufacturer is not in SubPUMP databank, this field is required._x000a_-------_x000a_Manufacturers in SubPUMP:_x000a_Almaz, Alnas, Borets, CAI, Centrilift/ODI or CLift, ESP, Lemaz, Novomet, Novo, ODI, Schlumberger/Reda or Reda, Weatherford or Wford, WSP" sqref="W179:W1103 V175:V178 V118:V149 V161:V173 V152:V159" xr:uid="{9A547A56-E420-4C2C-BE7C-866904004891}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Manufacturer Name" prompt="Select a manufacturer from the list, or enter a new manufacturer using a short name" sqref="B179:B1103 A152:A178" xr:uid="{730E29A7-E193-4760-8A9E-D7881A70E46B}">
+      <formula1>$A$1009:$A$1021</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/app_unified/dist/PUMPS (1).xlsx
+++ b/app_unified/dist/PUMPS (1).xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\OneDrive\Desktop\ESP DESING ESTUDIO\app_unified\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E36F49-F0FA-450F-9DEB-2D8748DE0FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EF2173-DF3D-4E0B-9B95-B2ED56E31FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{FC341EB1-65C7-47F8-9E2D-590F22EBE9EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{FC341EB1-65C7-47F8-9E2D-590F22EBE9EA}"/>
   </bookViews>
   <sheets>
     <sheet name="PUMP" sheetId="1" r:id="rId1"/>
     <sheet name="MOTORS" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MOTORS!$A$3:$AH$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MOTORS!$A$3:$AH$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PUMP!$A$2:$AJ$2</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -312,7 +313,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="641">
   <si>
     <t>Required Pump data</t>
   </si>
@@ -1113,9 +1114,6 @@
     <t>NH(1500-2500)H</t>
   </si>
   <si>
-    <t>ALK</t>
-  </si>
-  <si>
     <t>WD1000ZX(N)</t>
   </si>
   <si>
@@ -1644,55 +1642,19 @@
     <t>WSP</t>
   </si>
   <si>
-    <t>XT1-S</t>
-  </si>
-  <si>
     <t>456</t>
-  </si>
-  <si>
-    <t>XT2-S</t>
-  </si>
-  <si>
-    <t>XT1-T</t>
-  </si>
-  <si>
-    <t>XT1-D</t>
   </si>
   <si>
     <t>550</t>
   </si>
   <si>
-    <t>XT1</t>
-  </si>
-  <si>
-    <t>XT1-s</t>
-  </si>
-  <si>
-    <t>PMM HV</t>
-  </si>
-  <si>
-    <t>PMM LV</t>
-  </si>
-  <si>
-    <t>PMM</t>
-  </si>
-  <si>
-    <t>XT3-T</t>
-  </si>
-  <si>
     <t>FLEX47</t>
-  </si>
-  <si>
-    <t>BH</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
     <t>FlEX27</t>
-  </si>
-  <si>
-    <t>FlexER</t>
   </si>
   <si>
     <t>64.36</t>
@@ -1836,9 +1798,6 @@
     <t>Schlumberger</t>
   </si>
   <si>
-    <t>DN 1050</t>
-  </si>
-  <si>
     <t>71.2</t>
   </si>
   <si>
@@ -1867,9 +1826,6 @@
   </si>
   <si>
     <t>1.0</t>
-  </si>
-  <si>
-    <t>DN 1400</t>
   </si>
   <si>
     <t>72.5</t>
@@ -1932,12 +1888,6 @@
     <t>3.12e-15</t>
   </si>
   <si>
-    <t>DN 1750</t>
-  </si>
-  <si>
-    <t>DN 1800</t>
-  </si>
-  <si>
     <t>74.2</t>
   </si>
   <si>
@@ -1970,6 +1920,375 @@
   <si>
     <t>2.85e-15</t>
   </si>
+  <si>
+    <t>DN1050</t>
+  </si>
+  <si>
+    <t>DN1400</t>
+  </si>
+  <si>
+    <t>DN1750</t>
+  </si>
+  <si>
+    <t>DN1800</t>
+  </si>
+  <si>
+    <t>BakerHughes</t>
+  </si>
+  <si>
+    <t>Alkhorayef</t>
+  </si>
+  <si>
+    <t>XT1-S 330HP 1950V 102,5AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 287HP 1567V 92,5967749220832AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 782HP 2773V 160,8AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 730HP 2844V 155AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 391HP 1454V 160,8AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 104HP 2832V 22AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 391HP 2287V 92,5967749220832AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 574HP 3547V 92,5967749220832AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 574HP 3311V 92,5967749220832AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 391HP 3564V 92,6AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 574HP 3462V 92,5967749220832AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 287HP 1731V 92,5967749220832AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 391HP 2217V 92,5967749220832AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 15HP 2043V 92,5967749220832AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 400HP 3354V 74AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 206HP 1330V 99AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 110HP 2184V 33AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 90HP 2245V 28,4AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 105HP 2144V 32AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 43,5HP 1330V 23,0203754473066AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 339HP 3019V 57,8AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 391HP 3210V 66,4AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 339HP 3352V 57,8AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 365HP 3156V 66,4AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 261HP 2032V 66,4AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 157HP 2962V 30,7AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 287HP 3255V 51,5AMP</t>
+  </si>
+  <si>
+    <t>XT2-S 150HP 3190V 29AMP</t>
+  </si>
+  <si>
+    <t>XT1-T 240HP 2854V 46AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 391HP 3303V 66,4AMP</t>
+  </si>
+  <si>
+    <t>XT1-T 626HP 3018V 116,5AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 783HP 3454V 132,8AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 522HP 3062V 92,6AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 313HP 3093V 57,8AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 183HP 3384V 30,7AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 450HP 3032V 86,7AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 157HP 3032V 30,7AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 261HP 2303V 66,4AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 287HP 3112V 51,5AMP</t>
+  </si>
+  <si>
+    <t>XT1-D 574HP 3001V 92,5967749220832AMP</t>
+  </si>
+  <si>
+    <t>XT1-D 730HP 3497V 116,1AMP</t>
+  </si>
+  <si>
+    <t>XT1-D 470HP 3342V 78,1AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 183HP 3303V 30,7AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 157HP 2662V 30,7AMP</t>
+  </si>
+  <si>
+    <t>XT1-T 574HP 3497V 92,5967749220832AMP</t>
+  </si>
+  <si>
+    <t>XT1-D 626HP 3096V 116,5AMP</t>
+  </si>
+  <si>
+    <t>XT1-D 320HP 2068V 99AMP</t>
+  </si>
+  <si>
+    <t>XT1-D 298HP 2924V 65AMP</t>
+  </si>
+  <si>
+    <t>XT1-T 1350HP 4575V 177AMP</t>
+  </si>
+  <si>
+    <t>XT1 120HP 1855V 41AMP</t>
+  </si>
+  <si>
+    <t>XT1-s 261HP 1454V 92,5967749220832AMP</t>
+  </si>
+  <si>
+    <t>XT1 200HP 2012V 46AMP</t>
+  </si>
+  <si>
+    <t>XT1-s 230HP 3112V 43,4AMP</t>
+  </si>
+  <si>
+    <t>XT1-s 235HP 3144V 44AMP</t>
+  </si>
+  <si>
+    <t>XT1-s 130HP 1256V 57,8AMP</t>
+  </si>
+  <si>
+    <t>XT1-S 391HP 1948V 92,6AMP</t>
+  </si>
+  <si>
+    <t>XT1-D 412HP 3356V 78,5AMP</t>
+  </si>
+  <si>
+    <t>PMM HV 16HP 504V 17,2AMP</t>
+  </si>
+  <si>
+    <t>PMM LV 16HP 396V 21,7AMP</t>
+  </si>
+  <si>
+    <t>PMM HV 32HP 1008V 17AMP</t>
+  </si>
+  <si>
+    <t>PMM LV 32HP 792V 21,5AMP</t>
+  </si>
+  <si>
+    <t>PMM HV 48,276792HP 1500V 16,9AMP</t>
+  </si>
+  <si>
+    <t>PMM LV 48,276792HP 1200V 21,4AMP</t>
+  </si>
+  <si>
+    <t>PMM HV 64,369056HP 2040V 16,9AMP</t>
+  </si>
+  <si>
+    <t>PMM LV 64,369056HP 1560V 21,4AMP</t>
+  </si>
+  <si>
+    <t>PMM HV 80,46132HP 2520V 16,8AMP</t>
+  </si>
+  <si>
+    <t>PMM LV 80,46132HP 1980V 21,4AMP</t>
+  </si>
+  <si>
+    <t>PMM HV 96,553584HP 3000V 16,8AMP</t>
+  </si>
+  <si>
+    <t>PMM LV 96,553584HP 2400V 21,4AMP</t>
+  </si>
+  <si>
+    <t>PMM HV 112,645848HP 2760V 21,4AMP</t>
+  </si>
+  <si>
+    <t>PMM LV 112,645848HP 2280V 26,3AMP</t>
+  </si>
+  <si>
+    <t>PMM HV 128,738112HP 2880V 23,7AMP</t>
+  </si>
+  <si>
+    <t>PMM LV 128,738112HP 2280V 29,5AMP</t>
+  </si>
+  <si>
+    <t>PMM HV 144,830376HP 2520V 28,8AMP</t>
+  </si>
+  <si>
+    <t>PMM LV 144,830376HP 1920V 38,6AMP</t>
+  </si>
+  <si>
+    <t>PMM HV 160,92264HP 2880V 29,6AMP</t>
+  </si>
+  <si>
+    <t>PMM LV 160,92264HP 2160V 39,7AMP</t>
+  </si>
+  <si>
+    <t>PMM HV 177,014904HP 3000V 29,1AMP</t>
+  </si>
+  <si>
+    <t>PMM LV 177,014904HP 2280V 39,2AMP</t>
+  </si>
+  <si>
+    <t>PMM 193,107168HP 2520V 39AMP</t>
+  </si>
+  <si>
+    <t>PMM 209,199432HP 2760V 39AMP</t>
+  </si>
+  <si>
+    <t>PMM HV 241,38396HP 2940V 43,3AMP</t>
+  </si>
+  <si>
+    <t>PMM LV 241,38396HP 2400V 55,3AMP</t>
+  </si>
+  <si>
+    <t>PMM 281,61462HP 2760V 52,2AMP</t>
+  </si>
+  <si>
+    <t>PMM 324HP 3261V 54,2AMP</t>
+  </si>
+  <si>
+    <t>PMM 370HP 3360V 57,1AMP</t>
+  </si>
+  <si>
+    <t>PMM 402HP 3720V 57AMP</t>
+  </si>
+  <si>
+    <t>XT3-T 1173HP 4362V 160,8AMP</t>
+  </si>
+  <si>
+    <t>FLEXER</t>
+  </si>
+  <si>
+    <t>WE-8000</t>
+  </si>
+  <si>
+    <t>S8000N</t>
+  </si>
+  <si>
+    <t>6.44E+01</t>
+  </si>
+  <si>
+    <t>1.90E+00</t>
+  </si>
+  <si>
+    <t>3.05E-04</t>
+  </si>
+  <si>
+    <t>-9.94E-07</t>
+  </si>
+  <si>
+    <t>2.35E-10</t>
+  </si>
+  <si>
+    <t>-2.43E-14</t>
+  </si>
+  <si>
+    <t>7.62E-19</t>
+  </si>
+  <si>
+    <t>1.91E-04</t>
+  </si>
+  <si>
+    <t>2.31E-08</t>
+  </si>
+  <si>
+    <t>-1.34E-12</t>
+  </si>
+  <si>
+    <t>-1.84E-16</t>
+  </si>
+  <si>
+    <t>8.35E-21</t>
+  </si>
+  <si>
+    <t>E8000</t>
+  </si>
+  <si>
+    <t>7.70E+01</t>
+  </si>
+  <si>
+    <t>-1.90E-03</t>
+  </si>
+  <si>
+    <t>-2.74E-07</t>
+  </si>
+  <si>
+    <t>3.67E-11</t>
+  </si>
+  <si>
+    <t>-4.04E-15</t>
+  </si>
+  <si>
+    <t>9.29E-20</t>
+  </si>
+  <si>
+    <t>2.92E+00</t>
+  </si>
+  <si>
+    <t>3.26E-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -1.12E-07</t>
+  </si>
+  <si>
+    <t>2.07E-11</t>
+  </si>
+  <si>
+    <t>-1.61E-15</t>
+  </si>
+  <si>
+    <t>4.31E-20</t>
+  </si>
+  <si>
+    <t>WE-2700</t>
+  </si>
 </sst>
 </file>
 
@@ -1980,7 +2299,7 @@
     <numFmt numFmtId="165" formatCode="0.00000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2102,6 +2421,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -2214,7 +2539,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2595,6 +2920,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="11" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -11908,7 +12280,7 @@
     </row>
     <row r="92" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B92" s="89" t="s">
         <v>83</v>
@@ -12010,7 +12382,7 @@
     </row>
     <row r="93" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B93" s="89" t="s">
         <v>83</v>
@@ -12112,7 +12484,7 @@
     </row>
     <row r="94" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B94" s="89" t="s">
         <v>83</v>
@@ -12214,7 +12586,7 @@
     </row>
     <row r="95" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A95" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B95" s="89" t="s">
         <v>83</v>
@@ -12316,7 +12688,7 @@
     </row>
     <row r="96" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A96" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B96" s="89" t="s">
         <v>119</v>
@@ -12418,7 +12790,7 @@
     </row>
     <row r="97" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A97" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B97" s="89" t="s">
         <v>119</v>
@@ -12520,7 +12892,7 @@
     </row>
     <row r="98" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A98" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B98" s="89" t="s">
         <v>119</v>
@@ -12622,7 +12994,7 @@
     </row>
     <row r="99" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A99" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B99" s="89" t="s">
         <v>119</v>
@@ -12724,7 +13096,7 @@
     </row>
     <row r="100" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A100" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B100" s="89" t="s">
         <v>119</v>
@@ -12826,7 +13198,7 @@
     </row>
     <row r="101" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A101" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B101" s="93" t="s">
         <v>119</v>
@@ -12928,7 +13300,7 @@
     </row>
     <row r="102" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A102" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B102" s="93" t="s">
         <v>119</v>
@@ -13030,7 +13402,7 @@
     </row>
     <row r="103" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B103" s="68" t="s">
         <v>119</v>
@@ -13132,7 +13504,7 @@
     </row>
     <row r="104" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B104" s="93" t="s">
         <v>119</v>
@@ -13234,7 +13606,7 @@
     </row>
     <row r="105" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A105" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B105" s="68" t="s">
         <v>119</v>
@@ -13336,7 +13708,7 @@
     </row>
     <row r="106" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A106" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B106" s="93" t="s">
         <v>119</v>
@@ -13438,7 +13810,7 @@
     </row>
     <row r="107" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A107" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B107" s="68" t="s">
         <v>119</v>
@@ -13540,7 +13912,7 @@
     </row>
     <row r="108" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B108" s="88" t="s">
         <v>132</v>
@@ -13642,7 +14014,7 @@
     </row>
     <row r="109" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B109" s="88" t="s">
         <v>132</v>
@@ -13744,7 +14116,7 @@
     </row>
     <row r="110" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B110" s="93" t="s">
         <v>132</v>
@@ -13846,7 +14218,7 @@
     </row>
     <row r="111" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B111" s="93">
         <v>513</v>
@@ -13948,7 +14320,7 @@
     </row>
     <row r="112" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B112" s="93" t="s">
         <v>132</v>
@@ -14050,7 +14422,7 @@
     </row>
     <row r="113" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B113" s="93" t="s">
         <v>132</v>
@@ -14152,7 +14524,7 @@
     </row>
     <row r="114" spans="1:36" s="27" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B114" s="93" t="s">
         <v>132</v>
@@ -14254,7 +14626,7 @@
     </row>
     <row r="115" spans="1:36" s="27" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B115" s="93" t="s">
         <v>140</v>
@@ -14356,7 +14728,7 @@
     </row>
     <row r="116" spans="1:36" s="27" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B116" s="93" t="s">
         <v>140</v>
@@ -14458,7 +14830,7 @@
     </row>
     <row r="117" spans="1:36" s="28" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B117" s="93" t="s">
         <v>140</v>
@@ -14560,7 +14932,7 @@
     </row>
     <row r="118" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A118" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B118" s="93" t="s">
         <v>140</v>
@@ -14662,7 +15034,7 @@
     </row>
     <row r="119" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B119" s="93" t="s">
         <v>140</v>
@@ -14764,7 +15136,7 @@
     </row>
     <row r="120" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B120" s="93" t="s">
         <v>140</v>
@@ -14866,7 +15238,7 @@
     </row>
     <row r="121" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B121" s="93" t="s">
         <v>140</v>
@@ -14968,7 +15340,7 @@
     </row>
     <row r="122" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B122" s="93" t="s">
         <v>140</v>
@@ -15070,7 +15442,7 @@
     </row>
     <row r="123" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B123" s="93" t="s">
         <v>149</v>
@@ -15172,7 +15544,7 @@
     </row>
     <row r="124" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B124" s="93" t="s">
         <v>149</v>
@@ -15274,7 +15646,7 @@
     </row>
     <row r="125" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B125" s="93" t="s">
         <v>149</v>
@@ -15376,7 +15748,7 @@
     </row>
     <row r="126" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B126" s="93" t="s">
         <v>153</v>
@@ -15472,7 +15844,7 @@
     </row>
     <row r="127" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B127" s="93" t="s">
         <v>153</v>
@@ -15568,7 +15940,7 @@
     </row>
     <row r="128" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B128" s="93" t="s">
         <v>153</v>
@@ -15664,7 +16036,7 @@
     </row>
     <row r="129" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B129" s="93" t="s">
         <v>153</v>
@@ -15760,7 +16132,7 @@
     </row>
     <row r="130" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B130" s="93" t="s">
         <v>158</v>
@@ -15856,7 +16228,7 @@
     </row>
     <row r="131" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B131" s="93" t="s">
         <v>158</v>
@@ -15952,7 +16324,7 @@
     </row>
     <row r="132" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B132" s="93" t="s">
         <v>158</v>
@@ -16048,7 +16420,7 @@
     </row>
     <row r="133" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B133" s="93" t="s">
         <v>158</v>
@@ -16144,7 +16516,7 @@
     </row>
     <row r="134" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B134" s="93" t="s">
         <v>158</v>
@@ -16240,7 +16612,7 @@
     </row>
     <row r="135" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B135" s="93" t="s">
         <v>158</v>
@@ -16336,7 +16708,7 @@
     </row>
     <row r="136" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B136" s="93" t="s">
         <v>165</v>
@@ -16432,7 +16804,7 @@
     </row>
     <row r="137" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B137" s="93" t="s">
         <v>165</v>
@@ -16528,7 +16900,7 @@
     </row>
     <row r="138" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B138" s="93" t="s">
         <v>165</v>
@@ -16624,7 +16996,7 @@
     </row>
     <row r="139" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B139" s="93" t="s">
         <v>169</v>
@@ -16720,7 +17092,7 @@
     </row>
     <row r="140" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B140" s="93" t="s">
         <v>169</v>
@@ -16816,7 +17188,7 @@
     </row>
     <row r="141" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B141" s="93" t="s">
         <v>172</v>
@@ -16912,13 +17284,13 @@
     </row>
     <row r="142" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B142" s="93" t="s">
         <v>119</v>
       </c>
       <c r="C142" s="93" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D142" s="93">
         <v>500</v>
@@ -17014,13 +17386,13 @@
     </row>
     <row r="143" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B143" s="93" t="s">
         <v>140</v>
       </c>
       <c r="C143" s="93" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D143" s="93">
         <v>650</v>
@@ -17116,13 +17488,13 @@
     </row>
     <row r="144" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B144" s="93" t="s">
         <v>140</v>
       </c>
       <c r="C144" s="93" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D144" s="93">
         <v>2000</v>
@@ -17218,13 +17590,13 @@
     </row>
     <row r="145" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B145" s="93" t="s">
         <v>83</v>
       </c>
       <c r="C145" s="93" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D145" s="93">
         <v>600</v>
@@ -17320,7 +17692,7 @@
     </row>
     <row r="146" spans="1:36" s="99" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B146" s="93" t="s">
         <v>140</v>
@@ -17412,7 +17784,7 @@
     </row>
     <row r="147" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B147" s="93" t="s">
         <v>83</v>
@@ -17514,7 +17886,7 @@
     </row>
     <row r="148" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B148" s="93" t="s">
         <v>83</v>
@@ -17616,7 +17988,7 @@
     </row>
     <row r="149" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="14" t="s">
-        <v>249</v>
+        <v>523</v>
       </c>
       <c r="B149" s="93" t="s">
         <v>83</v>
@@ -17718,13 +18090,13 @@
     </row>
     <row r="150" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="14" t="s">
-        <v>439</v>
+        <v>522</v>
       </c>
       <c r="B150" s="93">
         <v>538</v>
       </c>
       <c r="C150" s="93" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="D150" s="93">
         <v>1500</v>
@@ -17816,13 +18188,13 @@
     </row>
     <row r="151" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="14" t="s">
-        <v>439</v>
+        <v>522</v>
       </c>
       <c r="B151" s="93">
         <v>538</v>
       </c>
       <c r="C151" s="93" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="D151" s="93">
         <v>750</v>
@@ -17888,39 +18260,39 @@
         <v>5627</v>
       </c>
       <c r="Y151" s="100" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="Z151" s="82">
         <v>0.875</v>
       </c>
       <c r="AA151" s="100" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AB151" s="100" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AC151" s="101" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AD151" s="101" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AE151" s="101" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AF151" s="98" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
     </row>
     <row r="152" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="14" t="s">
-        <v>439</v>
+        <v>522</v>
       </c>
       <c r="B152" s="93">
         <v>400</v>
       </c>
       <c r="C152" s="93" t="s">
-        <v>442</v>
+        <v>612</v>
       </c>
       <c r="D152" s="93">
         <v>50</v>
@@ -17932,10 +18304,10 @@
         <v>2900</v>
       </c>
       <c r="G152" s="93" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="H152" s="93" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="I152" s="93">
         <v>2900</v>
@@ -17944,40 +18316,40 @@
         <v>60</v>
       </c>
       <c r="K152" s="78" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="L152" s="78" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="M152" s="78" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="N152" s="78" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="O152" s="78" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="P152" s="78" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="Q152" s="78" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="R152" s="78" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="S152" s="78" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="T152" s="78" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="U152" s="78" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="V152" s="78" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="W152" s="80">
         <v>4</v>
@@ -17986,39 +18358,39 @@
         <v>5627</v>
       </c>
       <c r="Y152" s="100" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="Z152" s="82" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AA152" s="100" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AB152" s="100" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AC152" s="101" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AD152" s="101" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AE152" s="101" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AF152" s="98" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
     </row>
     <row r="153" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="68" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="B153" s="93">
         <v>538</v>
       </c>
       <c r="C153" s="93" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="D153" s="93">
         <v>1000</v>
@@ -18030,10 +18402,10 @@
         <v>6000</v>
       </c>
       <c r="G153" s="93" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="H153" s="93" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="I153" s="93">
         <v>7500</v>
@@ -18042,81 +18414,81 @@
         <v>60</v>
       </c>
       <c r="K153" s="78" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="L153" s="78" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="M153" s="78" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="N153" s="78" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="O153" s="78" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="P153" s="78" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="Q153" s="78" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="R153" s="78" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="S153" s="78" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="T153" s="78" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="U153" s="78" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="V153" s="78" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="W153" s="80" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="X153" s="100" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="Y153" s="100" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="Z153" s="82" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AA153" s="100" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AB153" s="100" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AC153" s="101" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AD153" s="101" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AE153" s="101" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="AF153" s="98" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
     </row>
     <row r="154" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="14" t="s">
-        <v>439</v>
+        <v>522</v>
       </c>
       <c r="B154" s="93">
         <v>538</v>
       </c>
       <c r="C154" s="93" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="D154" s="93">
         <v>200</v>
@@ -18128,10 +18500,10 @@
         <v>2250</v>
       </c>
       <c r="G154" s="93" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="H154" s="93" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="I154" s="93">
         <v>3000</v>
@@ -18140,664 +18512,900 @@
         <v>60</v>
       </c>
       <c r="K154" s="78" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="L154" s="78" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="M154" s="78" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="N154" s="78" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="O154" s="78" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="P154" s="78" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="Q154" s="78" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="R154" s="78" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="S154" s="78" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="T154" s="78" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="U154" s="78" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="V154" s="78" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="W154" s="80" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="X154" s="100">
         <v>5627</v>
       </c>
       <c r="Y154" s="100" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="Z154" s="82" t="s">
+        <v>475</v>
+      </c>
+      <c r="AA154" s="100" t="s">
+        <v>428</v>
+      </c>
+      <c r="AB154" s="100" t="s">
+        <v>428</v>
+      </c>
+      <c r="AC154" s="101" t="s">
+        <v>428</v>
+      </c>
+      <c r="AD154" s="101" t="s">
+        <v>428</v>
+      </c>
+      <c r="AE154" s="101" t="s">
+        <v>428</v>
+      </c>
+      <c r="AF154" s="98" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="155" spans="1:36" s="124" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="115" t="s">
+        <v>476</v>
+      </c>
+      <c r="B155" s="116">
+        <v>400</v>
+      </c>
+      <c r="C155" s="116" t="s">
+        <v>518</v>
+      </c>
+      <c r="D155" s="116">
+        <v>300</v>
+      </c>
+      <c r="E155" s="116">
+        <v>1050</v>
+      </c>
+      <c r="F155" s="116">
+        <v>1650</v>
+      </c>
+      <c r="G155" s="116" t="s">
+        <v>477</v>
+      </c>
+      <c r="H155" s="116" t="s">
+        <v>478</v>
+      </c>
+      <c r="I155" s="116">
+        <v>1800</v>
+      </c>
+      <c r="J155" s="117" t="s">
+        <v>478</v>
+      </c>
+      <c r="K155" s="118" t="s">
+        <v>479</v>
+      </c>
+      <c r="L155" s="118">
+        <v>-1.54E-2</v>
+      </c>
+      <c r="M155" s="118">
+        <v>6.2099999999999998E-6</v>
+      </c>
+      <c r="N155" s="118">
+        <v>-1.03E-9</v>
+      </c>
+      <c r="O155" s="118">
+        <v>0</v>
+      </c>
+      <c r="P155" s="118" t="s">
+        <v>480</v>
+      </c>
+      <c r="Q155" s="118" t="s">
+        <v>481</v>
+      </c>
+      <c r="R155" s="118">
+        <v>1.12E-4</v>
+      </c>
+      <c r="S155" s="118">
+        <v>-4.1299999999999999E-8</v>
+      </c>
+      <c r="T155" s="118" t="s">
+        <v>482</v>
+      </c>
+      <c r="U155" s="118">
+        <v>0</v>
+      </c>
+      <c r="V155" s="118" t="s">
+        <v>483</v>
+      </c>
+      <c r="W155" s="119">
+        <v>5000</v>
+      </c>
+      <c r="X155" s="120">
+        <v>6000</v>
+      </c>
+      <c r="Y155" s="120" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z155" s="121">
+        <v>154</v>
+      </c>
+      <c r="AA155" s="120">
+        <v>240</v>
+      </c>
+      <c r="AB155" s="120">
+        <v>1</v>
+      </c>
+      <c r="AC155" s="122">
+        <v>400</v>
+      </c>
+      <c r="AD155" s="122">
+        <v>1</v>
+      </c>
+      <c r="AE155" s="122">
+        <v>105</v>
+      </c>
+      <c r="AF155" s="123" t="s">
+        <v>485</v>
+      </c>
+      <c r="AG155" s="124">
+        <v>1050</v>
+      </c>
+      <c r="AH155" s="124" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="156" spans="1:36" s="124" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="115" t="s">
+        <v>476</v>
+      </c>
+      <c r="B156" s="116">
+        <v>400</v>
+      </c>
+      <c r="C156" s="116" t="s">
+        <v>519</v>
+      </c>
+      <c r="D156" s="116">
+        <v>400</v>
+      </c>
+      <c r="E156" s="116">
+        <v>1400</v>
+      </c>
+      <c r="F156" s="116">
+        <v>2200</v>
+      </c>
+      <c r="G156" s="116" t="s">
+        <v>487</v>
+      </c>
+      <c r="H156" s="116" t="s">
         <v>488</v>
       </c>
-      <c r="AA154" s="100" t="s">
-        <v>440</v>
-      </c>
-      <c r="AB154" s="100" t="s">
-        <v>440</v>
-      </c>
-      <c r="AC154" s="101" t="s">
-        <v>440</v>
-      </c>
-      <c r="AD154" s="101" t="s">
-        <v>440</v>
-      </c>
-      <c r="AE154" s="101" t="s">
-        <v>440</v>
-      </c>
-      <c r="AF154" s="98" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="155" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="68" t="s">
+      <c r="I156" s="116">
+        <v>2500</v>
+      </c>
+      <c r="J156" s="117" t="s">
+        <v>488</v>
+      </c>
+      <c r="K156" s="118" t="s">
         <v>489</v>
       </c>
-      <c r="B155" s="93">
+      <c r="L156" s="118">
+        <v>-1.1299999999999999E-2</v>
+      </c>
+      <c r="M156" s="118" t="s">
+        <v>490</v>
+      </c>
+      <c r="N156" s="118" t="s">
+        <v>491</v>
+      </c>
+      <c r="O156" s="118">
+        <v>0</v>
+      </c>
+      <c r="P156" s="118" t="s">
+        <v>492</v>
+      </c>
+      <c r="Q156" s="118" t="s">
+        <v>493</v>
+      </c>
+      <c r="R156" s="118" t="s">
+        <v>494</v>
+      </c>
+      <c r="S156" s="118" t="s">
+        <v>495</v>
+      </c>
+      <c r="T156" s="118">
+        <v>4.2200000000000002E-12</v>
+      </c>
+      <c r="U156" s="118">
+        <v>0</v>
+      </c>
+      <c r="V156" s="118" t="s">
+        <v>483</v>
+      </c>
+      <c r="W156" s="119">
+        <v>5000</v>
+      </c>
+      <c r="X156" s="120">
+        <v>6000</v>
+      </c>
+      <c r="Y156" s="120" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z156" s="121">
+        <v>154</v>
+      </c>
+      <c r="AA156" s="120">
+        <v>240</v>
+      </c>
+      <c r="AB156" s="120">
+        <v>1</v>
+      </c>
+      <c r="AC156" s="122">
         <v>400</v>
       </c>
-      <c r="C155" s="93" t="s">
-        <v>490</v>
-      </c>
-      <c r="D155" s="93">
+      <c r="AD156" s="122">
+        <v>1</v>
+      </c>
+      <c r="AE156" s="122">
+        <v>163</v>
+      </c>
+      <c r="AF156" s="123" t="s">
+        <v>485</v>
+      </c>
+      <c r="AG156" s="124">
+        <v>1400</v>
+      </c>
+      <c r="AH156" s="124" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="157" spans="1:36" s="124" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="115" t="s">
+        <v>476</v>
+      </c>
+      <c r="B157" s="116">
+        <v>400</v>
+      </c>
+      <c r="C157" s="116" t="s">
+        <v>520</v>
+      </c>
+      <c r="D157" s="116">
+        <v>500</v>
+      </c>
+      <c r="E157" s="116">
+        <v>1750</v>
+      </c>
+      <c r="F157" s="116">
+        <v>2700</v>
+      </c>
+      <c r="G157" s="116" t="s">
+        <v>496</v>
+      </c>
+      <c r="H157" s="116" t="s">
+        <v>497</v>
+      </c>
+      <c r="I157" s="116">
+        <v>3000</v>
+      </c>
+      <c r="J157" s="117" t="s">
+        <v>497</v>
+      </c>
+      <c r="K157" s="118" t="s">
+        <v>498</v>
+      </c>
+      <c r="L157" s="118" t="s">
+        <v>499</v>
+      </c>
+      <c r="M157" s="118" t="s">
+        <v>500</v>
+      </c>
+      <c r="N157" s="118" t="s">
+        <v>501</v>
+      </c>
+      <c r="O157" s="118">
+        <v>0</v>
+      </c>
+      <c r="P157" s="118" t="s">
+        <v>502</v>
+      </c>
+      <c r="Q157" s="118" t="s">
+        <v>503</v>
+      </c>
+      <c r="R157" s="118" t="s">
+        <v>504</v>
+      </c>
+      <c r="S157" s="118" t="s">
+        <v>505</v>
+      </c>
+      <c r="T157" s="118" t="s">
+        <v>506</v>
+      </c>
+      <c r="U157" s="118">
+        <v>0</v>
+      </c>
+      <c r="V157" s="118" t="s">
+        <v>483</v>
+      </c>
+      <c r="W157" s="119">
+        <v>5000</v>
+      </c>
+      <c r="X157" s="120">
+        <v>6000</v>
+      </c>
+      <c r="Y157" s="120" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z157" s="121">
+        <v>154</v>
+      </c>
+      <c r="AA157" s="120">
+        <v>240</v>
+      </c>
+      <c r="AB157" s="120">
+        <v>1</v>
+      </c>
+      <c r="AC157" s="122">
+        <v>400</v>
+      </c>
+      <c r="AD157" s="122">
+        <v>1</v>
+      </c>
+      <c r="AE157" s="122">
+        <v>93</v>
+      </c>
+      <c r="AF157" s="123" t="s">
+        <v>485</v>
+      </c>
+      <c r="AG157" s="124">
+        <v>1750</v>
+      </c>
+      <c r="AH157" s="124" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="158" spans="1:36" s="124" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="115" t="s">
+        <v>476</v>
+      </c>
+      <c r="B158" s="116">
+        <v>400</v>
+      </c>
+      <c r="C158" s="116" t="s">
+        <v>521</v>
+      </c>
+      <c r="D158" s="116">
+        <v>600</v>
+      </c>
+      <c r="E158" s="116">
+        <v>1800</v>
+      </c>
+      <c r="F158" s="116">
+        <v>2850</v>
+      </c>
+      <c r="G158" s="116" t="s">
+        <v>507</v>
+      </c>
+      <c r="H158" s="116" t="s">
+        <v>508</v>
+      </c>
+      <c r="I158" s="116">
+        <v>3200</v>
+      </c>
+      <c r="J158" s="117" t="s">
+        <v>508</v>
+      </c>
+      <c r="K158" s="118" t="s">
+        <v>509</v>
+      </c>
+      <c r="L158" s="118" t="s">
+        <v>510</v>
+      </c>
+      <c r="M158" s="118" t="s">
+        <v>511</v>
+      </c>
+      <c r="N158" s="118" t="s">
+        <v>512</v>
+      </c>
+      <c r="O158" s="118">
+        <v>0</v>
+      </c>
+      <c r="P158" s="118" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q158" s="118" t="s">
+        <v>514</v>
+      </c>
+      <c r="R158" s="118" t="s">
+        <v>515</v>
+      </c>
+      <c r="S158" s="118" t="s">
+        <v>516</v>
+      </c>
+      <c r="T158" s="118" t="s">
+        <v>517</v>
+      </c>
+      <c r="U158" s="118">
+        <v>0</v>
+      </c>
+      <c r="V158" s="118" t="s">
+        <v>483</v>
+      </c>
+      <c r="W158" s="119">
+        <v>5000</v>
+      </c>
+      <c r="X158" s="120">
+        <v>6000</v>
+      </c>
+      <c r="Y158" s="120" t="s">
+        <v>484</v>
+      </c>
+      <c r="Z158" s="121">
+        <v>154</v>
+      </c>
+      <c r="AA158" s="120">
+        <v>240</v>
+      </c>
+      <c r="AB158" s="120">
+        <v>1</v>
+      </c>
+      <c r="AC158" s="122">
+        <v>400</v>
+      </c>
+      <c r="AD158" s="122">
+        <v>1</v>
+      </c>
+      <c r="AE158" s="122">
+        <v>117</v>
+      </c>
+      <c r="AF158" s="123" t="s">
+        <v>485</v>
+      </c>
+      <c r="AG158" s="124">
+        <v>1800</v>
+      </c>
+      <c r="AH158" s="124" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="159" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="B159" s="93">
+        <v>538</v>
+      </c>
+      <c r="C159" s="93" t="s">
+        <v>613</v>
+      </c>
+      <c r="D159" s="93">
+        <v>2000</v>
+      </c>
+      <c r="E159" s="93">
+        <v>8000</v>
+      </c>
+      <c r="F159" s="93">
+        <v>10500</v>
+      </c>
+      <c r="G159" s="93">
+        <v>0.8</v>
+      </c>
+      <c r="H159" s="93">
+        <v>74.650000000000006</v>
+      </c>
+      <c r="I159" s="93">
+        <v>12900</v>
+      </c>
+      <c r="J159" s="72">
+        <v>60</v>
+      </c>
+      <c r="K159" s="78">
+        <v>71</v>
+      </c>
+      <c r="L159" s="78">
+        <v>7.9399999999999991E-3</v>
+      </c>
+      <c r="M159" s="78">
+        <v>-5.2299999999999999E-6</v>
+      </c>
+      <c r="N159" s="78">
+        <v>1.01E-9</v>
+      </c>
+      <c r="O159" s="78">
+        <v>-8.4899999999999997E-14</v>
+      </c>
+      <c r="P159" s="78">
+        <v>2.46E-18</v>
+      </c>
+      <c r="Q159" s="78">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="R159" s="78">
+        <v>3.21E-4</v>
+      </c>
+      <c r="S159" s="78">
+        <v>-6.5400000000000003E-8</v>
+      </c>
+      <c r="T159" s="78">
+        <v>1.1300000000000001E-11</v>
+      </c>
+      <c r="U159" s="78">
+        <v>-9.2400000000000003E-16</v>
+      </c>
+      <c r="V159" s="78">
+        <v>2.5500000000000001E-20</v>
+      </c>
+      <c r="W159" s="80">
+        <v>5.38</v>
+      </c>
+      <c r="X159" s="100">
+        <v>5000</v>
+      </c>
+      <c r="Y159" s="100">
+        <v>6000</v>
+      </c>
+      <c r="Z159" s="82">
+        <v>0.88</v>
+      </c>
+      <c r="AA159" s="100">
+        <v>400</v>
+      </c>
+      <c r="AB159" s="100">
+        <v>500</v>
+      </c>
+      <c r="AC159" s="101">
+        <v>3</v>
+      </c>
+      <c r="AD159" s="101">
+        <v>72</v>
+      </c>
+      <c r="AE159" s="101">
+        <v>5</v>
+      </c>
+      <c r="AF159" s="98">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="160" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="14" t="s">
+        <v>476</v>
+      </c>
+      <c r="B160" s="93">
+        <v>538</v>
+      </c>
+      <c r="C160" s="93" t="s">
+        <v>614</v>
+      </c>
+      <c r="D160" s="93">
+        <v>3500</v>
+      </c>
+      <c r="E160" s="93">
+        <v>8000</v>
+      </c>
+      <c r="F160" s="93">
+        <v>10500</v>
+      </c>
+      <c r="G160" s="93">
+        <v>77.2</v>
+      </c>
+      <c r="H160" s="93">
+        <v>64.367000000000004</v>
+      </c>
+      <c r="I160" s="93">
+        <v>12500</v>
+      </c>
+      <c r="J160" s="72">
+        <v>60</v>
+      </c>
+      <c r="K160" s="78" t="s">
+        <v>615</v>
+      </c>
+      <c r="L160" s="78" t="s">
+        <v>617</v>
+      </c>
+      <c r="M160" s="78" t="s">
+        <v>618</v>
+      </c>
+      <c r="N160" s="78" t="s">
+        <v>619</v>
+      </c>
+      <c r="O160" s="78" t="s">
+        <v>620</v>
+      </c>
+      <c r="P160" s="78" t="s">
+        <v>621</v>
+      </c>
+      <c r="Q160" s="44" t="s">
+        <v>616</v>
+      </c>
+      <c r="R160" s="78" t="s">
+        <v>622</v>
+      </c>
+      <c r="S160" s="78" t="s">
+        <v>623</v>
+      </c>
+      <c r="T160" s="78" t="s">
+        <v>624</v>
+      </c>
+      <c r="U160" s="78" t="s">
+        <v>625</v>
+      </c>
+      <c r="V160" s="78" t="s">
+        <v>626</v>
+      </c>
+      <c r="W160" s="80">
+        <v>5.38</v>
+      </c>
+      <c r="X160" s="100">
+        <v>5000</v>
+      </c>
+      <c r="Y160" s="100">
+        <v>7500</v>
+      </c>
+      <c r="Z160" s="82">
+        <v>1</v>
+      </c>
+      <c r="AA160" s="100">
+        <v>3.8</v>
+      </c>
+      <c r="AB160" s="100">
+        <v>5.2</v>
+      </c>
+      <c r="AC160" s="101">
+        <v>1</v>
+      </c>
+      <c r="AD160" s="101">
+        <v>500</v>
+      </c>
+      <c r="AE160" s="101">
+        <v>1</v>
+      </c>
+      <c r="AF160" s="98">
+        <v>5000</v>
+      </c>
+      <c r="AG160" s="44" t="s">
+        <v>485</v>
+      </c>
+      <c r="AH160" s="44" t="s">
+        <v>485</v>
+      </c>
+      <c r="AI160" s="44">
+        <v>0</v>
+      </c>
+      <c r="AJ160" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="B161" s="93">
+        <v>538</v>
+      </c>
+      <c r="C161" s="93" t="s">
+        <v>627</v>
+      </c>
+      <c r="D161" s="93">
+        <v>2200</v>
+      </c>
+      <c r="E161" s="93">
+        <v>7500</v>
+      </c>
+      <c r="F161" s="93">
+        <v>10500</v>
+      </c>
+      <c r="G161" s="93">
+        <v>77.22</v>
+      </c>
+      <c r="H161" s="93">
+        <v>77</v>
+      </c>
+      <c r="I161" s="93">
+        <v>12000</v>
+      </c>
+      <c r="J161" s="72">
+        <v>60</v>
+      </c>
+      <c r="K161" s="78" t="s">
+        <v>628</v>
+      </c>
+      <c r="L161" s="78" t="s">
+        <v>629</v>
+      </c>
+      <c r="M161" s="78" t="s">
+        <v>630</v>
+      </c>
+      <c r="N161" s="78" t="s">
+        <v>631</v>
+      </c>
+      <c r="O161" s="78" t="s">
+        <v>632</v>
+      </c>
+      <c r="P161" s="78" t="s">
+        <v>633</v>
+      </c>
+      <c r="Q161" s="44" t="s">
+        <v>634</v>
+      </c>
+      <c r="R161" s="78" t="s">
+        <v>635</v>
+      </c>
+      <c r="S161" s="78" t="s">
+        <v>636</v>
+      </c>
+      <c r="T161" s="78" t="s">
+        <v>637</v>
+      </c>
+      <c r="U161" s="78" t="s">
+        <v>638</v>
+      </c>
+      <c r="V161" s="78" t="s">
+        <v>639</v>
+      </c>
+      <c r="W161" s="80">
+        <v>5.38</v>
+      </c>
+      <c r="X161" s="100">
+        <v>5627</v>
+      </c>
+      <c r="Y161" s="100">
+        <v>7500</v>
+      </c>
+      <c r="Z161" s="82">
+        <v>0.875</v>
+      </c>
+      <c r="AA161" s="100">
+        <v>4</v>
+      </c>
+      <c r="AB161" s="100">
+        <v>5.5</v>
+      </c>
+      <c r="AC161" s="101">
+        <v>10</v>
+      </c>
+      <c r="AD161" s="101">
+        <v>60</v>
+      </c>
+      <c r="AE161" s="101"/>
+      <c r="AF161" s="98"/>
+    </row>
+    <row r="162" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="B162" s="93">
+        <v>538</v>
+      </c>
+      <c r="C162" s="93" t="s">
+        <v>640</v>
+      </c>
+      <c r="D162" s="93">
         <v>300</v>
       </c>
-      <c r="E155" s="93">
-        <v>1050</v>
-      </c>
-      <c r="F155" s="93">
-        <v>1650</v>
-      </c>
-      <c r="G155" s="93" t="s">
-        <v>491</v>
-      </c>
-      <c r="H155" s="93" t="s">
-        <v>492</v>
-      </c>
-      <c r="I155" s="93">
-        <v>1800</v>
-      </c>
-      <c r="J155" s="72" t="s">
-        <v>492</v>
-      </c>
-      <c r="K155" s="78" t="s">
-        <v>493</v>
-      </c>
-      <c r="L155" s="78">
-        <v>-1.54E-2</v>
-      </c>
-      <c r="M155" s="78">
-        <v>6.2099999999999998E-6</v>
-      </c>
-      <c r="N155" s="78">
-        <v>-1.03E-9</v>
-      </c>
-      <c r="O155" s="78">
-        <v>0</v>
-      </c>
-      <c r="P155" s="78" t="s">
-        <v>494</v>
-      </c>
-      <c r="Q155" s="78" t="s">
-        <v>495</v>
-      </c>
-      <c r="R155" s="78">
-        <v>1.12E-4</v>
-      </c>
-      <c r="S155" s="78">
-        <v>-4.1299999999999999E-8</v>
-      </c>
-      <c r="T155" s="78" t="s">
-        <v>496</v>
-      </c>
-      <c r="U155" s="78">
-        <v>0</v>
-      </c>
-      <c r="V155" s="78" t="s">
-        <v>497</v>
-      </c>
-      <c r="W155" s="80">
+      <c r="E162" s="93">
+        <v>2716</v>
+      </c>
+      <c r="F162" s="93">
+        <v>3500</v>
+      </c>
+      <c r="G162" s="93">
+        <v>0.7</v>
+      </c>
+      <c r="H162" s="93">
+        <v>71.709999999999994</v>
+      </c>
+      <c r="I162" s="93">
+        <v>4850</v>
+      </c>
+      <c r="J162" s="72">
+        <v>60</v>
+      </c>
+      <c r="K162" s="78">
+        <v>71.7</v>
+      </c>
+      <c r="L162" s="78">
+        <v>-6.6800000000000002E-3</v>
+      </c>
+      <c r="M162" s="78">
+        <v>6.9600000000000003E-6</v>
+      </c>
+      <c r="N162" s="78">
+        <v>-4.6800000000000004E-9</v>
+      </c>
+      <c r="O162" s="78">
+        <v>9.8800000000000003E-13</v>
+      </c>
+      <c r="P162" s="78">
+        <v>-7.9900000000000002E-17</v>
+      </c>
+      <c r="Q162" s="44">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="R162" s="78">
+        <v>2.7500000000000001E-5</v>
+      </c>
+      <c r="S162" s="78">
+        <v>3.3799999999999998E-7</v>
+      </c>
+      <c r="T162" s="78">
+        <v>-1.7800000000000001E-10</v>
+      </c>
+      <c r="U162" s="78">
+        <v>3.7499999999999998E-14</v>
+      </c>
+      <c r="V162" s="78">
+        <v>-2.9799999999999999E-18</v>
+      </c>
+      <c r="W162" s="80">
+        <v>5.38</v>
+      </c>
+      <c r="X162" s="100">
         <v>5000</v>
       </c>
-      <c r="X155" s="100">
+      <c r="Y162" s="100">
         <v>6000</v>
       </c>
-      <c r="Y155" s="100" t="s">
-        <v>498</v>
-      </c>
-      <c r="Z155" s="82">
-        <v>154</v>
-      </c>
-      <c r="AA155" s="100">
-        <v>240</v>
-      </c>
-      <c r="AB155" s="100">
-        <v>1</v>
-      </c>
-      <c r="AC155" s="101">
+      <c r="Z162" s="82">
+        <v>0.88</v>
+      </c>
+      <c r="AA162" s="100">
+        <v>250</v>
+      </c>
+      <c r="AB162" s="100">
         <v>400</v>
       </c>
-      <c r="AD155" s="101">
-        <v>1</v>
-      </c>
-      <c r="AE155" s="101">
-        <v>105</v>
-      </c>
-      <c r="AF155" s="98" t="s">
-        <v>499</v>
-      </c>
-      <c r="AG155" s="44">
-        <v>1050</v>
-      </c>
-      <c r="AH155" s="44" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="156" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="68" t="s">
-        <v>489</v>
-      </c>
-      <c r="B156" s="93">
-        <v>400</v>
-      </c>
-      <c r="C156" s="93" t="s">
-        <v>501</v>
-      </c>
-      <c r="D156" s="93">
-        <v>400</v>
-      </c>
-      <c r="E156" s="93">
-        <v>1400</v>
-      </c>
-      <c r="F156" s="93">
-        <v>2200</v>
-      </c>
-      <c r="G156" s="93" t="s">
-        <v>502</v>
-      </c>
-      <c r="H156" s="93" t="s">
-        <v>503</v>
-      </c>
-      <c r="I156" s="93">
-        <v>2500</v>
-      </c>
-      <c r="J156" s="72" t="s">
-        <v>503</v>
-      </c>
-      <c r="K156" s="78" t="s">
-        <v>504</v>
-      </c>
-      <c r="L156" s="78">
-        <v>-1.1299999999999999E-2</v>
-      </c>
-      <c r="M156" s="78" t="s">
-        <v>505</v>
-      </c>
-      <c r="N156" s="78" t="s">
-        <v>506</v>
-      </c>
-      <c r="O156" s="78">
-        <v>0</v>
-      </c>
-      <c r="P156" s="78" t="s">
-        <v>507</v>
-      </c>
-      <c r="Q156" s="78" t="s">
-        <v>508</v>
-      </c>
-      <c r="R156" s="78" t="s">
-        <v>509</v>
-      </c>
-      <c r="S156" s="78" t="s">
-        <v>510</v>
-      </c>
-      <c r="T156" s="78">
-        <v>4.2200000000000002E-12</v>
-      </c>
-      <c r="U156" s="78">
-        <v>0</v>
-      </c>
-      <c r="V156" s="78" t="s">
-        <v>497</v>
-      </c>
-      <c r="W156" s="80">
-        <v>5000</v>
-      </c>
-      <c r="X156" s="100">
-        <v>6000</v>
-      </c>
-      <c r="Y156" s="100" t="s">
-        <v>498</v>
-      </c>
-      <c r="Z156" s="82">
-        <v>154</v>
-      </c>
-      <c r="AA156" s="100">
-        <v>240</v>
-      </c>
-      <c r="AB156" s="100">
-        <v>1</v>
-      </c>
-      <c r="AC156" s="101">
-        <v>400</v>
-      </c>
-      <c r="AD156" s="101">
-        <v>1</v>
-      </c>
-      <c r="AE156" s="101">
-        <v>163</v>
-      </c>
-      <c r="AF156" s="98" t="s">
-        <v>499</v>
-      </c>
-      <c r="AG156" s="44">
-        <v>1400</v>
-      </c>
-      <c r="AH156" s="44" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="157" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="68" t="s">
-        <v>489</v>
-      </c>
-      <c r="B157" s="93">
-        <v>400</v>
-      </c>
-      <c r="C157" s="93" t="s">
-        <v>522</v>
-      </c>
-      <c r="D157" s="93">
-        <v>500</v>
-      </c>
-      <c r="E157" s="93">
-        <v>1750</v>
-      </c>
-      <c r="F157" s="93">
-        <v>2700</v>
-      </c>
-      <c r="G157" s="93" t="s">
-        <v>511</v>
-      </c>
-      <c r="H157" s="93" t="s">
-        <v>512</v>
-      </c>
-      <c r="I157" s="93">
-        <v>3000</v>
-      </c>
-      <c r="J157" s="72" t="s">
-        <v>512</v>
-      </c>
-      <c r="K157" s="78" t="s">
-        <v>513</v>
-      </c>
-      <c r="L157" s="78" t="s">
-        <v>514</v>
-      </c>
-      <c r="M157" s="78" t="s">
-        <v>515</v>
-      </c>
-      <c r="N157" s="78" t="s">
-        <v>516</v>
-      </c>
-      <c r="O157" s="78">
-        <v>0</v>
-      </c>
-      <c r="P157" s="78" t="s">
-        <v>517</v>
-      </c>
-      <c r="Q157" s="78" t="s">
-        <v>518</v>
-      </c>
-      <c r="R157" s="78" t="s">
-        <v>519</v>
-      </c>
-      <c r="S157" s="78" t="s">
-        <v>520</v>
-      </c>
-      <c r="T157" s="78" t="s">
-        <v>521</v>
-      </c>
-      <c r="U157" s="78">
-        <v>0</v>
-      </c>
-      <c r="V157" s="78" t="s">
-        <v>497</v>
-      </c>
-      <c r="W157" s="80">
-        <v>5000</v>
-      </c>
-      <c r="X157" s="100">
-        <v>6000</v>
-      </c>
-      <c r="Y157" s="100" t="s">
-        <v>498</v>
-      </c>
-      <c r="Z157" s="82">
-        <v>154</v>
-      </c>
-      <c r="AA157" s="100">
-        <v>240</v>
-      </c>
-      <c r="AB157" s="100">
-        <v>1</v>
-      </c>
-      <c r="AC157" s="101">
-        <v>400</v>
-      </c>
-      <c r="AD157" s="101">
-        <v>1</v>
-      </c>
-      <c r="AE157" s="101">
-        <v>93</v>
-      </c>
-      <c r="AF157" s="98" t="s">
-        <v>499</v>
-      </c>
-      <c r="AG157" s="44">
-        <v>1750</v>
-      </c>
-      <c r="AH157" s="44" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="158" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="68" t="s">
-        <v>489</v>
-      </c>
-      <c r="B158" s="93">
-        <v>400</v>
-      </c>
-      <c r="C158" s="93" t="s">
-        <v>523</v>
-      </c>
-      <c r="D158" s="93">
-        <v>600</v>
-      </c>
-      <c r="E158" s="93">
-        <v>1800</v>
-      </c>
-      <c r="F158" s="93">
-        <v>2850</v>
-      </c>
-      <c r="G158" s="93" t="s">
-        <v>524</v>
-      </c>
-      <c r="H158" s="93" t="s">
-        <v>525</v>
-      </c>
-      <c r="I158" s="93">
-        <v>3200</v>
-      </c>
-      <c r="J158" s="72" t="s">
-        <v>525</v>
-      </c>
-      <c r="K158" s="78" t="s">
-        <v>526</v>
-      </c>
-      <c r="L158" s="78" t="s">
-        <v>527</v>
-      </c>
-      <c r="M158" s="78" t="s">
-        <v>528</v>
-      </c>
-      <c r="N158" s="78" t="s">
-        <v>529</v>
-      </c>
-      <c r="O158" s="78">
-        <v>0</v>
-      </c>
-      <c r="P158" s="78" t="s">
-        <v>530</v>
-      </c>
-      <c r="Q158" s="78" t="s">
-        <v>531</v>
-      </c>
-      <c r="R158" s="78" t="s">
-        <v>532</v>
-      </c>
-      <c r="S158" s="78" t="s">
-        <v>533</v>
-      </c>
-      <c r="T158" s="78" t="s">
-        <v>534</v>
-      </c>
-      <c r="U158" s="78">
-        <v>0</v>
-      </c>
-      <c r="V158" s="78" t="s">
-        <v>497</v>
-      </c>
-      <c r="W158" s="80">
-        <v>5000</v>
-      </c>
-      <c r="X158" s="100">
-        <v>6000</v>
-      </c>
-      <c r="Y158" s="100" t="s">
-        <v>498</v>
-      </c>
-      <c r="Z158" s="82">
-        <v>154</v>
-      </c>
-      <c r="AA158" s="100">
-        <v>240</v>
-      </c>
-      <c r="AB158" s="100">
-        <v>1</v>
-      </c>
-      <c r="AC158" s="101">
-        <v>400</v>
-      </c>
-      <c r="AD158" s="101">
-        <v>1</v>
-      </c>
-      <c r="AE158" s="101">
-        <v>117</v>
-      </c>
-      <c r="AF158" s="98" t="s">
-        <v>499</v>
-      </c>
-      <c r="AG158" s="44">
-        <v>1800</v>
-      </c>
-      <c r="AH158" s="44" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="159" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="32"/>
-      <c r="B159" s="27"/>
-      <c r="C159" s="33"/>
-      <c r="D159" s="27"/>
-      <c r="E159" s="27"/>
-      <c r="F159" s="27"/>
-      <c r="G159" s="27"/>
-      <c r="H159" s="27"/>
-      <c r="J159" s="24"/>
-      <c r="L159" s="24"/>
-      <c r="M159" s="24"/>
-      <c r="N159" s="24"/>
-      <c r="O159" s="24"/>
-      <c r="P159" s="24"/>
-      <c r="R159" s="24"/>
-      <c r="S159" s="24"/>
-      <c r="T159" s="24"/>
-      <c r="U159" s="24"/>
-      <c r="V159" s="24"/>
-      <c r="W159" s="29"/>
-      <c r="X159" s="30"/>
-      <c r="Y159" s="30"/>
-      <c r="Z159" s="26"/>
-      <c r="AA159" s="30"/>
-      <c r="AB159" s="30"/>
-      <c r="AC159" s="31"/>
-      <c r="AD159" s="31"/>
-      <c r="AE159" s="31"/>
-      <c r="AF159" s="36"/>
-    </row>
-    <row r="160" spans="1:36" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="32"/>
-      <c r="B160" s="27"/>
-      <c r="C160" s="33"/>
-      <c r="D160" s="27"/>
-      <c r="E160" s="27"/>
-      <c r="F160" s="27"/>
-      <c r="G160" s="27"/>
-      <c r="H160" s="27"/>
-      <c r="J160" s="24"/>
-      <c r="L160" s="24"/>
-      <c r="M160" s="24"/>
-      <c r="N160" s="24"/>
-      <c r="O160" s="24"/>
-      <c r="P160" s="24"/>
-      <c r="Q160" s="24"/>
-      <c r="R160" s="24"/>
-      <c r="S160" s="24"/>
-      <c r="T160" s="24"/>
-      <c r="U160" s="24"/>
-      <c r="V160" s="24"/>
-      <c r="W160" s="29"/>
-      <c r="X160" s="30"/>
-      <c r="Y160" s="30"/>
-      <c r="Z160" s="26"/>
-      <c r="AA160" s="30"/>
-      <c r="AB160" s="30"/>
-      <c r="AC160" s="31"/>
-      <c r="AD160" s="31"/>
-      <c r="AE160" s="31"/>
-      <c r="AF160" s="36"/>
-    </row>
-    <row r="161" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="32"/>
-      <c r="B161" s="27"/>
-      <c r="C161" s="33"/>
-      <c r="D161" s="27"/>
-      <c r="E161" s="27"/>
-      <c r="F161" s="27"/>
-      <c r="G161" s="27"/>
-      <c r="H161" s="27"/>
-      <c r="J161" s="24"/>
-      <c r="K161" s="24"/>
-      <c r="L161" s="24"/>
-      <c r="M161" s="24"/>
-      <c r="N161" s="24"/>
-      <c r="O161" s="24"/>
-      <c r="P161" s="24"/>
-      <c r="Q161" s="24"/>
-      <c r="R161" s="24"/>
-      <c r="S161" s="24"/>
-      <c r="T161" s="24"/>
-      <c r="U161" s="24"/>
-      <c r="V161" s="24"/>
-      <c r="W161" s="29"/>
-      <c r="X161" s="30"/>
-      <c r="Y161" s="30"/>
-      <c r="Z161" s="26"/>
-      <c r="AA161" s="30"/>
-      <c r="AB161" s="30"/>
-      <c r="AC161" s="31"/>
-      <c r="AD161" s="31"/>
-      <c r="AE161" s="31"/>
-      <c r="AF161" s="36"/>
-    </row>
-    <row r="162" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="32"/>
-      <c r="B162" s="27"/>
-      <c r="C162" s="33"/>
-      <c r="D162" s="27"/>
-      <c r="E162" s="27"/>
-      <c r="F162" s="27"/>
-      <c r="G162" s="27"/>
-      <c r="H162" s="27"/>
-      <c r="I162" s="24"/>
-      <c r="J162" s="27"/>
-      <c r="K162" s="24"/>
-      <c r="L162" s="24"/>
-      <c r="M162" s="24"/>
-      <c r="N162" s="24"/>
-      <c r="O162" s="24"/>
-      <c r="P162" s="24"/>
-      <c r="Q162" s="24"/>
-      <c r="R162" s="24"/>
-      <c r="S162" s="24"/>
-      <c r="T162" s="24"/>
-      <c r="U162" s="24"/>
-      <c r="V162" s="24"/>
-      <c r="W162" s="29"/>
-      <c r="X162" s="30"/>
-      <c r="Y162" s="30"/>
-      <c r="Z162" s="26"/>
-      <c r="AA162" s="30"/>
-      <c r="AB162" s="30"/>
-      <c r="AC162" s="31"/>
-      <c r="AD162" s="31"/>
-      <c r="AE162" s="31"/>
-      <c r="AF162" s="36"/>
-    </row>
-    <row r="163" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="32"/>
-      <c r="B163" s="27"/>
-      <c r="C163" s="33"/>
-      <c r="D163" s="27"/>
-      <c r="E163" s="27"/>
-      <c r="F163" s="27"/>
-      <c r="G163" s="27"/>
-      <c r="H163" s="27"/>
-      <c r="I163" s="27"/>
-      <c r="J163" s="27"/>
-      <c r="K163" s="24"/>
-      <c r="L163" s="24"/>
-      <c r="M163" s="24"/>
-      <c r="N163" s="24"/>
-      <c r="O163" s="24"/>
-      <c r="P163" s="24"/>
-      <c r="Q163" s="24"/>
-      <c r="R163" s="24"/>
-      <c r="S163" s="24"/>
-      <c r="T163" s="24"/>
-      <c r="U163" s="24"/>
-      <c r="V163" s="24"/>
-      <c r="W163" s="29"/>
-      <c r="X163" s="30"/>
-      <c r="Y163" s="30"/>
-      <c r="Z163" s="26"/>
-      <c r="AA163" s="30"/>
-      <c r="AB163" s="30"/>
-      <c r="AC163" s="31"/>
-      <c r="AD163" s="31"/>
-      <c r="AE163" s="31"/>
-      <c r="AF163" s="36"/>
+      <c r="AC162" s="101">
+        <v>5</v>
+      </c>
+      <c r="AD162" s="101">
+        <v>98</v>
+      </c>
+      <c r="AE162" s="101">
+        <v>7</v>
+      </c>
+      <c r="AF162" s="98">
+        <v>18000</v>
+      </c>
     </row>
     <row r="164" spans="1:34" s="44" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="32"/>
       <c r="B164" s="27"/>
       <c r="C164" s="33"/>
       <c r="D164" s="27"/>
-      <c r="E164" s="27"/>
+      <c r="E164" s="126"/>
       <c r="F164" s="27"/>
       <c r="G164" s="27"/>
       <c r="H164" s="27"/>
       <c r="I164" s="27"/>
       <c r="J164" s="27"/>
-      <c r="K164" s="24"/>
+      <c r="K164" s="125"/>
       <c r="L164" s="24"/>
       <c r="M164" s="24"/>
       <c r="N164" s="24"/>
@@ -50938,16 +51546,17 @@
       <c r="AG1104" s="36"/>
     </row>
   </sheetData>
+  <autoFilter ref="A2:AJ2" xr:uid="{053E6D0B-9E01-4484-8758-0E93695A87D4}"/>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter 1 for gas handler" sqref="AH5:AH117" xr:uid="{D4F63CA9-4B8A-4E8D-8A06-46E288212DB9}">
       <formula1>$A$1000:$A$1001</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter 1 for obsolete" sqref="AG5:AG117 AF152:AF178 AF118:AF149 AG179:AG1103" xr:uid="{6AE47EA0-4762-42E9-B62C-07E716141A03}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter 1 for obsolete" sqref="AG5:AG117 AF118:AF149 AG179:AG1103 AF152:AF162 AF164:AF178" xr:uid="{6AE47EA0-4762-42E9-B62C-07E716141A03}">
       <formula1>$A$1000:$A$1001</formula1>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Important Notice:" prompt="If a manufacturer is not the SubPUMP databank, this field is required. The available manufacturers within SubPUMP can be found in the drop down list in the manufacturer field (Column B)." sqref="W39 W82:W97 W7:W34 W42:W77 W79:W80 W99:W100 W103:W117" xr:uid="{3ABA8888-4F6D-4392-92AF-AB8BE0A86DDD}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Important Notice:" prompt="-------_x000a_If a manufacturer is not in SubPUMP databank, this field is required._x000a_-------_x000a_Manufacturers in SubPUMP:_x000a_Almaz, Alnas, Borets, CAI, Centrilift/ODI or CLift, ESP, Lemaz, Novomet, Novo, ODI, Schlumberger/Reda or Reda, Weatherford or Wford, WSP" sqref="W179:W1103 V175:V178 V118:V149 V161:V173 V152:V159" xr:uid="{9A547A56-E420-4C2C-BE7C-866904004891}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Manufacturer Name" prompt="Select a manufacturer from the list, or enter a new manufacturer using a short name" sqref="B179:B1103 A152:A178" xr:uid="{730E29A7-E193-4760-8A9E-D7881A70E46B}">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Important Notice:" prompt="-------_x000a_If a manufacturer is not in SubPUMP databank, this field is required._x000a_-------_x000a_Manufacturers in SubPUMP:_x000a_Almaz, Alnas, Borets, CAI, Centrilift/ODI or CLift, ESP, Lemaz, Novomet, Novo, ODI, Schlumberger/Reda or Reda, Weatherford or Wford, WSP" sqref="W179:W1103 V175:V178 V118:V149 W159 V152:V158 W162 V161:V162 V164:V173" xr:uid="{9A547A56-E420-4C2C-BE7C-866904004891}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Manufacturer Name" prompt="Select a manufacturer from the list, or enter a new manufacturer using a short name" sqref="B179:B1103 A153 A155:A160 A162 A164:A178" xr:uid="{730E29A7-E193-4760-8A9E-D7881A70E46B}">
       <formula1>$A$1009:$A$1021</formula1>
     </dataValidation>
   </dataValidations>
@@ -50964,6 +51573,7 @@
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="114"/>
+    <col min="3" max="3" width="23.44140625" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="17.44140625" bestFit="1" customWidth="1"/>
@@ -50979,54 +51589,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="128" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="116"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="117" t="s">
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="129" t="s">
         <v>179</v>
       </c>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="118" t="s">
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="130" t="s">
         <v>180</v>
       </c>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="117" t="s">
+      <c r="O1" s="130"/>
+      <c r="P1" s="130"/>
+      <c r="Q1" s="130"/>
+      <c r="R1" s="130"/>
+      <c r="S1" s="130"/>
+      <c r="T1" s="129" t="s">
         <v>181</v>
       </c>
-      <c r="U1" s="117"/>
-      <c r="V1" s="117"/>
-      <c r="W1" s="117"/>
-      <c r="X1" s="117"/>
-      <c r="Y1" s="117"/>
-      <c r="Z1" s="118" t="s">
+      <c r="U1" s="129"/>
+      <c r="V1" s="129"/>
+      <c r="W1" s="129"/>
+      <c r="X1" s="129"/>
+      <c r="Y1" s="129"/>
+      <c r="Z1" s="130" t="s">
         <v>182</v>
       </c>
-      <c r="AA1" s="118"/>
-      <c r="AB1" s="118"/>
-      <c r="AC1" s="118"/>
-      <c r="AD1" s="118"/>
-      <c r="AE1" s="118"/>
-      <c r="AF1" s="115" t="s">
+      <c r="AA1" s="130"/>
+      <c r="AB1" s="130"/>
+      <c r="AC1" s="130"/>
+      <c r="AD1" s="130"/>
+      <c r="AE1" s="130"/>
+      <c r="AF1" s="127" t="s">
         <v>183</v>
       </c>
-      <c r="AG1" s="115"/>
-      <c r="AH1" s="115"/>
-      <c r="AI1" s="115"/>
-      <c r="AJ1" s="115"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" s="55" t="s">
@@ -51193,10 +51803,10 @@
         <v>59</v>
       </c>
       <c r="B4" s="110" t="s">
+        <v>253</v>
+      </c>
+      <c r="C4" s="57" t="s">
         <v>254</v>
-      </c>
-      <c r="C4" s="57" t="s">
-        <v>255</v>
       </c>
       <c r="D4" s="58">
         <v>10.7</v>
@@ -51297,10 +51907,10 @@
         <v>59</v>
       </c>
       <c r="B5" s="110" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C5" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D5" s="58">
         <v>14.3</v>
@@ -51401,10 +52011,10 @@
         <v>59</v>
       </c>
       <c r="B6" s="110" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C6" s="57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D6" s="58">
         <v>19</v>
@@ -51505,10 +52115,10 @@
         <v>59</v>
       </c>
       <c r="B7" s="110" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D7" s="58">
         <v>29.5</v>
@@ -51609,10 +52219,10 @@
         <v>59</v>
       </c>
       <c r="B8" s="110" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D8" s="58">
         <v>30.7</v>
@@ -51713,10 +52323,10 @@
         <v>59</v>
       </c>
       <c r="B9" s="110" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D9" s="58">
         <v>33</v>
@@ -51817,10 +52427,10 @@
         <v>59</v>
       </c>
       <c r="B10" s="110" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D10" s="58">
         <v>47.2</v>
@@ -51921,10 +52531,10 @@
         <v>59</v>
       </c>
       <c r="B11" s="110" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D11" s="58">
         <v>56.6</v>
@@ -52028,7 +52638,7 @@
         <v>97</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D12" s="58">
         <v>10.199999999999999</v>
@@ -52132,7 +52742,7 @@
         <v>97</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D13" s="58">
         <v>12.4</v>
@@ -52236,7 +52846,7 @@
         <v>97</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D14" s="58">
         <v>13.6</v>
@@ -52340,7 +52950,7 @@
         <v>97</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D15" s="58">
         <v>14.7</v>
@@ -52444,7 +53054,7 @@
         <v>97</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D16" s="58">
         <v>17</v>
@@ -52548,7 +53158,7 @@
         <v>97</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D17" s="58">
         <v>19.3</v>
@@ -52652,7 +53262,7 @@
         <v>97</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D18" s="58">
         <v>22.7</v>
@@ -52756,7 +53366,7 @@
         <v>97</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D19" s="58">
         <v>23.8</v>
@@ -52860,7 +53470,7 @@
         <v>97</v>
       </c>
       <c r="C20" s="57" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D20" s="58">
         <v>26.1</v>
@@ -52964,7 +53574,7 @@
         <v>97</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D21" s="58">
         <v>28.3</v>
@@ -53068,7 +53678,7 @@
         <v>97</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D22" s="58">
         <v>31.7</v>
@@ -53172,7 +53782,7 @@
         <v>97</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D23" s="58">
         <v>38.6</v>
@@ -53276,7 +53886,7 @@
         <v>97</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D24" s="58">
         <v>40.799999999999997</v>
@@ -53380,7 +53990,7 @@
         <v>97</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D25" s="58">
         <v>43.1</v>
@@ -53484,7 +54094,7 @@
         <v>97</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D26" s="58">
         <v>47.6</v>
@@ -53588,7 +54198,7 @@
         <v>97</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D27" s="58">
         <v>55.5</v>
@@ -53692,7 +54302,7 @@
         <v>97</v>
       </c>
       <c r="C28" s="57" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D28" s="58">
         <v>62.3</v>
@@ -53796,7 +54406,7 @@
         <v>97</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D29" s="58">
         <v>66.8</v>
@@ -53900,7 +54510,7 @@
         <v>213</v>
       </c>
       <c r="C30" s="57" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D30" s="58">
         <v>6.2</v>
@@ -54004,7 +54614,7 @@
         <v>213</v>
       </c>
       <c r="C31" s="57" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D31" s="58">
         <v>7.5</v>
@@ -54108,7 +54718,7 @@
         <v>213</v>
       </c>
       <c r="C32" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D32" s="58">
         <v>8.9</v>
@@ -54212,7 +54822,7 @@
         <v>213</v>
       </c>
       <c r="C33" s="104" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D33" s="63">
         <v>9.8000000000000007</v>
@@ -54313,7 +54923,7 @@
         <v>213</v>
       </c>
       <c r="C34" s="105" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D34" s="64">
         <v>11.2</v>
@@ -54414,7 +55024,7 @@
         <v>213</v>
       </c>
       <c r="C35" s="106" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D35" s="64">
         <v>12.5</v>
@@ -54515,7 +55125,7 @@
         <v>213</v>
       </c>
       <c r="C36" s="106" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D36" s="64">
         <v>13.8</v>
@@ -54616,7 +55226,7 @@
         <v>213</v>
       </c>
       <c r="C37" s="106" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D37" s="63">
         <v>15.1</v>
@@ -54717,7 +55327,7 @@
         <v>213</v>
       </c>
       <c r="C38" s="104" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D38" s="63">
         <v>16.100000000000001</v>
@@ -54818,7 +55428,7 @@
         <v>213</v>
       </c>
       <c r="C39" s="104" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D39" s="63">
         <v>17.399999999999999</v>
@@ -54919,7 +55529,7 @@
         <v>213</v>
       </c>
       <c r="C40" s="104" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D40" s="63">
         <v>20</v>
@@ -55020,7 +55630,7 @@
         <v>213</v>
       </c>
       <c r="C41" s="104" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D41" s="63">
         <v>21.3</v>
@@ -55121,7 +55731,7 @@
         <v>213</v>
       </c>
       <c r="C42" s="104" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D42" s="63">
         <v>22.3</v>
@@ -55222,7 +55832,7 @@
         <v>213</v>
       </c>
       <c r="C43" s="104" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D43" s="63">
         <v>24.9</v>
@@ -55323,7 +55933,7 @@
         <v>213</v>
       </c>
       <c r="C44" s="104" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D44" s="63">
         <v>24.9</v>
@@ -55424,7 +56034,7 @@
         <v>213</v>
       </c>
       <c r="C45" s="104" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D45" s="63">
         <v>28.5</v>
@@ -55525,7 +56135,7 @@
         <v>213</v>
       </c>
       <c r="C46" s="104" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D46" s="63">
         <v>34.5</v>
@@ -55626,7 +56236,7 @@
         <v>213</v>
       </c>
       <c r="C47" s="104" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D47" s="63">
         <v>34.5</v>
@@ -55727,7 +56337,7 @@
         <v>213</v>
       </c>
       <c r="C48" s="104" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D48" s="63">
         <v>39.700000000000003</v>
@@ -55828,7 +56438,7 @@
         <v>213</v>
       </c>
       <c r="C49" s="104" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D49" s="63">
         <v>42.3</v>
@@ -55929,7 +56539,7 @@
         <v>213</v>
       </c>
       <c r="C50" s="104" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D50" s="63">
         <v>44.6</v>
@@ -56030,7 +56640,7 @@
         <v>213</v>
       </c>
       <c r="C51" s="104" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D51" s="63">
         <v>48.5</v>
@@ -56131,7 +56741,7 @@
         <v>213</v>
       </c>
       <c r="C52" s="104" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D52" s="63">
         <v>52.1</v>
@@ -56232,7 +56842,7 @@
         <v>213</v>
       </c>
       <c r="C53" s="104" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D53" s="63">
         <v>53.1</v>
@@ -56333,7 +56943,7 @@
         <v>213</v>
       </c>
       <c r="C54" s="104" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D54" s="63">
         <v>55.2</v>
@@ -56434,7 +57044,7 @@
         <v>213</v>
       </c>
       <c r="C55" s="104" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D55" s="63">
         <v>61.7</v>
@@ -56535,7 +57145,7 @@
         <v>213</v>
       </c>
       <c r="C56" s="104" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D56" s="63">
         <v>66.900000000000006</v>
@@ -56636,7 +57246,7 @@
         <v>213</v>
       </c>
       <c r="C57" s="104" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D57" s="63">
         <v>73.099999999999994</v>
@@ -56737,7 +57347,7 @@
         <v>213</v>
       </c>
       <c r="C58" s="104" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D58" s="63">
         <v>56.7</v>
@@ -56838,7 +57448,7 @@
         <v>214</v>
       </c>
       <c r="C59" s="104" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D59" s="63">
         <v>9.3000000000000007</v>
@@ -56939,7 +57549,7 @@
         <v>214</v>
       </c>
       <c r="C60" s="104" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D60" s="63">
         <v>10.9</v>
@@ -57040,7 +57650,7 @@
         <v>214</v>
       </c>
       <c r="C61" s="104" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D61" s="63">
         <v>14.1</v>
@@ -57141,7 +57751,7 @@
         <v>214</v>
       </c>
       <c r="C62" s="104" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D62" s="63">
         <v>15.7</v>
@@ -57242,7 +57852,7 @@
         <v>214</v>
       </c>
       <c r="C63" s="104" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D63" s="63">
         <v>17.399999999999999</v>
@@ -57343,7 +57953,7 @@
         <v>214</v>
       </c>
       <c r="C64" s="104" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D64" s="63">
         <v>19</v>
@@ -57444,7 +58054,7 @@
         <v>214</v>
       </c>
       <c r="C65" s="104" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D65" s="63">
         <v>22.2</v>
@@ -57545,7 +58155,7 @@
         <v>214</v>
       </c>
       <c r="C66" s="104" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D66" s="63">
         <v>25.5</v>
@@ -57646,7 +58256,7 @@
         <v>214</v>
       </c>
       <c r="C67" s="104" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D67" s="63">
         <v>37.799999999999997</v>
@@ -57747,7 +58357,7 @@
         <v>214</v>
       </c>
       <c r="C68" s="104" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D68" s="63">
         <v>41</v>
@@ -57848,7 +58458,7 @@
         <v>214</v>
       </c>
       <c r="C69" s="104" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D69" s="63">
         <v>44.2</v>
@@ -57949,7 +58559,7 @@
         <v>214</v>
       </c>
       <c r="C70" s="104" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D70" s="63">
         <v>50.8</v>
@@ -58050,7 +58660,7 @@
         <v>214</v>
       </c>
       <c r="C71" s="104" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D71" s="63">
         <v>69.5</v>
@@ -58151,7 +58761,7 @@
         <v>214</v>
       </c>
       <c r="C72" s="104" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D72" s="63">
         <v>72.8</v>
@@ -58252,7 +58862,7 @@
         <v>214</v>
       </c>
       <c r="C73" s="104" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D73" s="63">
         <v>76.099999999999994</v>
@@ -58353,7 +58963,7 @@
         <v>149</v>
       </c>
       <c r="C74" s="104" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D74" s="63">
         <v>10.5</v>
@@ -58454,7 +59064,7 @@
         <v>149</v>
       </c>
       <c r="C75" s="104" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D75" s="63">
         <v>12</v>
@@ -58555,7 +59165,7 @@
         <v>149</v>
       </c>
       <c r="C76" s="104" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D76" s="63">
         <v>13.4</v>
@@ -58656,7 +59266,7 @@
         <v>149</v>
       </c>
       <c r="C77" s="104" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D77" s="63">
         <v>14.9</v>
@@ -58757,7 +59367,7 @@
         <v>149</v>
       </c>
       <c r="C78" s="107" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D78">
         <v>16.399999999999999</v>
@@ -58858,7 +59468,7 @@
         <v>149</v>
       </c>
       <c r="C79" s="107" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D79">
         <v>16.399999999999999</v>
@@ -58959,7 +59569,7 @@
         <v>149</v>
       </c>
       <c r="C80" s="107" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D80">
         <v>17.899999999999999</v>
@@ -59060,7 +59670,7 @@
         <v>149</v>
       </c>
       <c r="C81" s="107" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D81">
         <v>17.899999999999999</v>
@@ -59161,7 +59771,7 @@
         <v>149</v>
       </c>
       <c r="C82" s="107" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D82">
         <v>19.3</v>
@@ -59262,7 +59872,7 @@
         <v>149</v>
       </c>
       <c r="C83" s="107" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D83">
         <v>20.8</v>
@@ -59363,7 +59973,7 @@
         <v>149</v>
       </c>
       <c r="C84" s="107" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D84">
         <v>22.3</v>
@@ -59464,7 +60074,7 @@
         <v>149</v>
       </c>
       <c r="C85" s="107" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D85">
         <v>23.8</v>
@@ -59565,7 +60175,7 @@
         <v>149</v>
       </c>
       <c r="C86" s="107" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D86">
         <v>25.2</v>
@@ -59666,7 +60276,7 @@
         <v>149</v>
       </c>
       <c r="C87" s="107" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D87">
         <v>26.7</v>
@@ -59767,7 +60377,7 @@
         <v>149</v>
       </c>
       <c r="C88" s="107" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D88">
         <v>35.200000000000003</v>
@@ -59868,7 +60478,7 @@
         <v>149</v>
       </c>
       <c r="C89" s="107" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D89">
         <v>38.200000000000003</v>
@@ -59969,7 +60579,7 @@
         <v>149</v>
       </c>
       <c r="C90" s="107" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D90">
         <v>41.2</v>
@@ -60070,7 +60680,7 @@
         <v>149</v>
       </c>
       <c r="C91" s="107" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D91">
         <v>44.1</v>
@@ -60171,7 +60781,7 @@
         <v>149</v>
       </c>
       <c r="C92" s="107" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D92">
         <v>47</v>
@@ -60272,7 +60882,7 @@
         <v>149</v>
       </c>
       <c r="C93" s="107" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D93">
         <v>50</v>
@@ -60373,7 +60983,7 @@
         <v>149</v>
       </c>
       <c r="C94" s="107" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D94">
         <v>53</v>
@@ -60474,7 +61084,7 @@
         <v>149</v>
       </c>
       <c r="C95" s="107" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D95">
         <v>70.3</v>
@@ -60572,10 +61182,10 @@
         <v>59</v>
       </c>
       <c r="B96" s="114" t="s">
+        <v>340</v>
+      </c>
+      <c r="C96" s="107" t="s">
         <v>341</v>
-      </c>
-      <c r="C96" s="107" t="s">
-        <v>342</v>
       </c>
       <c r="D96">
         <v>11.8</v>
@@ -60673,10 +61283,10 @@
         <v>59</v>
       </c>
       <c r="B97" s="114" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C97" s="107" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D97">
         <v>13.5</v>
@@ -60774,10 +61384,10 @@
         <v>59</v>
       </c>
       <c r="B98" s="114" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C98" s="107" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D98">
         <v>16.399999999999999</v>
@@ -60875,10 +61485,10 @@
         <v>59</v>
       </c>
       <c r="B99" s="114" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C99" s="107" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D99">
         <v>20.7</v>
@@ -60976,10 +61586,10 @@
         <v>59</v>
       </c>
       <c r="B100" s="114" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C100" s="107" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D100">
         <v>27.2</v>
@@ -61077,10 +61687,10 @@
         <v>59</v>
       </c>
       <c r="B101" s="114" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C101" s="107" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D101">
         <v>36</v>
@@ -61178,10 +61788,10 @@
         <v>59</v>
       </c>
       <c r="B102" s="114" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C102" s="107" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D102">
         <v>45.2</v>
@@ -61282,7 +61892,7 @@
         <v>213</v>
       </c>
       <c r="C103" s="107" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D103">
         <v>9.5</v>
@@ -61383,7 +61993,7 @@
         <v>213</v>
       </c>
       <c r="C104" s="107" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D104">
         <v>8.1</v>
@@ -61484,7 +62094,7 @@
         <v>213</v>
       </c>
       <c r="C105" s="107" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D105">
         <v>6.8</v>
@@ -61585,7 +62195,7 @@
         <v>149</v>
       </c>
       <c r="C106" s="107" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D106">
         <v>50</v>
@@ -61686,7 +62296,7 @@
         <v>149</v>
       </c>
       <c r="C107" s="107" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D107">
         <v>53</v>
@@ -61787,7 +62397,7 @@
         <v>149</v>
       </c>
       <c r="C108" s="107" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D108">
         <v>70.3</v>
@@ -61885,10 +62495,10 @@
         <v>59</v>
       </c>
       <c r="B109" s="114" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C109" s="107" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D109">
         <v>60</v>
@@ -61986,10 +62596,10 @@
         <v>59</v>
       </c>
       <c r="B110" s="114" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C110" s="107" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D110">
         <v>60</v>
@@ -62087,10 +62697,10 @@
         <v>59</v>
       </c>
       <c r="B111" s="114" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C111" s="107" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D111">
         <v>60</v>
@@ -62191,7 +62801,7 @@
         <v>55</v>
       </c>
       <c r="C112" s="107" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D112">
         <v>44.9</v>
@@ -62292,7 +62902,7 @@
         <v>55</v>
       </c>
       <c r="C113" s="107" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D113">
         <v>6.9</v>
@@ -62393,7 +63003,7 @@
         <v>55</v>
       </c>
       <c r="C114" s="107" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D114">
         <v>8.9</v>
@@ -62494,7 +63104,7 @@
         <v>55</v>
       </c>
       <c r="C115" s="107" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D115">
         <v>10.8</v>
@@ -62595,7 +63205,7 @@
         <v>55</v>
       </c>
       <c r="C116" s="107" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D116">
         <v>12.7</v>
@@ -62696,7 +63306,7 @@
         <v>55</v>
       </c>
       <c r="C117" s="107" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D117">
         <v>14.7</v>
@@ -62797,7 +63407,7 @@
         <v>55</v>
       </c>
       <c r="C118" s="107" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D118">
         <v>16.600000000000001</v>
@@ -62898,7 +63508,7 @@
         <v>55</v>
       </c>
       <c r="C119" s="107" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D119">
         <v>17.600000000000001</v>
@@ -62999,7 +63609,7 @@
         <v>55</v>
       </c>
       <c r="C120" s="107" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D120">
         <v>18.5</v>
@@ -63100,7 +63710,7 @@
         <v>55</v>
       </c>
       <c r="C121" s="107" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D121">
         <v>20.399999999999999</v>
@@ -63201,7 +63811,7 @@
         <v>55</v>
       </c>
       <c r="C122" s="107" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D122">
         <v>31.5</v>
@@ -63302,7 +63912,7 @@
         <v>55</v>
       </c>
       <c r="C123" s="107" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D123">
         <v>33.299999999999997</v>
@@ -63403,7 +64013,7 @@
         <v>55</v>
       </c>
       <c r="C124" s="107" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D124">
         <v>35.299999999999997</v>
@@ -63504,7 +64114,7 @@
         <v>55</v>
       </c>
       <c r="C125" s="107" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D125">
         <v>39.1</v>
@@ -63605,7 +64215,7 @@
         <v>55</v>
       </c>
       <c r="C126" s="107" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D126">
         <v>41.1</v>
@@ -63706,7 +64316,7 @@
         <v>55</v>
       </c>
       <c r="C127" s="107" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D127">
         <v>43.1</v>
@@ -63807,7 +64417,7 @@
         <v>213</v>
       </c>
       <c r="C128" s="107" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D128">
         <v>6.8</v>
@@ -63900,7 +64510,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="129" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>59</v>
       </c>
@@ -63908,7 +64518,7 @@
         <v>214</v>
       </c>
       <c r="C129" s="107" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D129">
         <v>52</v>
@@ -64001,7 +64611,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="130" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>59</v>
       </c>
@@ -64009,7 +64619,7 @@
         <v>214</v>
       </c>
       <c r="C130" s="107" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D130">
         <v>45</v>
@@ -64102,7 +64712,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="131" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>59</v>
       </c>
@@ -64110,7 +64720,7 @@
         <v>214</v>
       </c>
       <c r="C131" s="107" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D131">
         <v>49</v>
@@ -64203,15 +64813,15 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="132" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>59</v>
       </c>
       <c r="B132" s="114" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C132" s="107" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D132">
         <v>33</v>
@@ -64304,7 +64914,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="133" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>59</v>
       </c>
@@ -64312,7 +64922,7 @@
         <v>213</v>
       </c>
       <c r="C133" s="107" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D133">
         <v>20.8</v>
@@ -64405,15 +65015,16 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="134" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>249</v>
+    <row r="134" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A134" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B134" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C134" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C134" s="107" t="str">
+        <f>AI134 &amp; " " &amp; E134 &amp; "HP " &amp; F134 &amp; "V " &amp; G134 &amp; "AMP"</f>
+        <v>SPECTRUM PMM 95,16HP 1658,4406779661V 31,2481481481482AMP</v>
       </c>
       <c r="D134">
         <v>6.1</v>
@@ -64508,16 +65119,20 @@
       <c r="AH134">
         <v>1200</v>
       </c>
-    </row>
-    <row r="135" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>249</v>
+      <c r="AI134" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="135" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A135" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B135" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C135" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C135" s="107" t="str">
+        <f t="shared" ref="C135:C156" si="0">AI135 &amp; " " &amp; E135 &amp; "HP " &amp; F135 &amp; "V " &amp; G135 &amp; "AMP"</f>
+        <v>SPECTRUM PMM 142,74HP 2487,66101694915V 31,2481481481481AMP</v>
       </c>
       <c r="D135">
         <v>7.6</v>
@@ -64612,16 +65227,20 @@
       <c r="AH135">
         <v>1200</v>
       </c>
-    </row>
-    <row r="136" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>249</v>
+      <c r="AI135" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="136" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A136" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B136" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C136" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C136" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 190,32HP 3316,8813559322V 31,2481481481482AMP</v>
       </c>
       <c r="D136">
         <v>9.1</v>
@@ -64716,16 +65335,20 @@
       <c r="AH136">
         <v>1200</v>
       </c>
-    </row>
-    <row r="137" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>249</v>
+      <c r="AI136" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="137" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A137" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B137" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C137" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C137" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 237,9HP 3777,5593220339V 34,2967479674797AMP</v>
       </c>
       <c r="D137">
         <v>10.6</v>
@@ -64820,16 +65443,20 @@
       <c r="AH137">
         <v>1200</v>
       </c>
-    </row>
-    <row r="138" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>249</v>
+      <c r="AI137" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="138" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A138" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B138" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C138" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C138" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 285,48HP 3943,40338983051V 39,4252336448598AMP</v>
       </c>
       <c r="D138">
         <v>12</v>
@@ -64924,16 +65551,20 @@
       <c r="AH138">
         <v>1200</v>
       </c>
-    </row>
-    <row r="139" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>249</v>
+      <c r="AI138" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="139" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A139" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B139" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C139" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C139" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 333,06HP 3912,69152542373V 46,3571428571429AMP</v>
       </c>
       <c r="D139">
         <v>13.5</v>
@@ -65028,16 +65659,20 @@
       <c r="AH139">
         <v>1200</v>
       </c>
-    </row>
-    <row r="140" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>249</v>
+      <c r="AI139" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="140" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A140" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B140" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C140" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C140" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 380,64HP 3881,97966101695V 53,3987341772152AMP</v>
       </c>
       <c r="D140">
         <v>15</v>
@@ -65132,16 +65767,20 @@
       <c r="AH140">
         <v>1200</v>
       </c>
-    </row>
-    <row r="141" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>249</v>
+      <c r="AI140" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="141" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A141" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B141" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C141" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C141" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 428,22HP 3924,97627118644V 59,4154929577465AMP</v>
       </c>
       <c r="D141">
         <v>16.399999999999999</v>
@@ -65236,16 +65875,20 @@
       <c r="AH141">
         <v>1200</v>
       </c>
-    </row>
-    <row r="142" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>249</v>
+      <c r="AI141" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="142" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A142" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B142" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C142" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C142" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 475,8HP 3869,69491525424V 66,9603174603175AMP</v>
       </c>
       <c r="D142">
         <v>17.899999999999999</v>
@@ -65340,16 +65983,20 @@
       <c r="AH142">
         <v>1200</v>
       </c>
-    </row>
-    <row r="143" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>249</v>
+      <c r="AI142" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="143" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A143" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B143" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C143" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C143" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 523,38HP 3986,4V 71,5AMP</v>
       </c>
       <c r="D143">
         <v>19.399999999999999</v>
@@ -65444,16 +66091,20 @@
       <c r="AH143">
         <v>1200</v>
       </c>
-    </row>
-    <row r="144" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>249</v>
+      <c r="AI143" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="144" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A144" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B144" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C144" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C144" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 570,96HP 3759,13220338983V 82,7156862745098AMP</v>
       </c>
       <c r="D144">
         <v>20.8</v>
@@ -65548,16 +66199,20 @@
       <c r="AH144">
         <v>1200</v>
       </c>
-    </row>
-    <row r="145" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>249</v>
+      <c r="AI144" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="145" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A145" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B145" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C145" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C145" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 618,54HP 3752,98983050847V 89,7553191489362AMP</v>
       </c>
       <c r="D145">
         <v>22.3</v>
@@ -65652,16 +66307,20 @@
       <c r="AH145">
         <v>1200</v>
       </c>
-    </row>
-    <row r="146" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>249</v>
+      <c r="AI145" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="146" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A146" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B146" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C146" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C146" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 666,12HP 3752,98983050847V 89,7553191489362AMP</v>
       </c>
       <c r="D146">
         <v>23.8</v>
@@ -65756,16 +66415,20 @@
       <c r="AH146">
         <v>1200</v>
       </c>
-    </row>
-    <row r="147" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>249</v>
+      <c r="AI146" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="147" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A147" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B147" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C147" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C147" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 713,7HP 3961,83050847458V 98,1046511627907AMP</v>
       </c>
       <c r="D147">
         <v>25.2</v>
@@ -65860,16 +66523,20 @@
       <c r="AH147">
         <v>1200</v>
       </c>
-    </row>
-    <row r="148" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>249</v>
+      <c r="AI147" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="148" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A148" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B148" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C148" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C148" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 761,28HP 3832,8406779661V 108,166666666667AMP</v>
       </c>
       <c r="D148">
         <v>26.7</v>
@@ -65964,16 +66631,20 @@
       <c r="AH148">
         <v>1200</v>
       </c>
-    </row>
-    <row r="149" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>249</v>
+      <c r="AI148" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="149" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A149" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B149" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C149" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C149" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 808,86HP 3654,71186440678V 120,528571428571AMP</v>
       </c>
       <c r="D149">
         <v>28.2</v>
@@ -66068,16 +66739,20 @@
       <c r="AH149">
         <v>1200</v>
       </c>
-    </row>
-    <row r="150" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>249</v>
+      <c r="AI149" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="150" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A150" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B150" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C150" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C150" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 856,44HP 3869,69491525424V 120,528571428571AMP</v>
       </c>
       <c r="D150">
         <v>29.6</v>
@@ -66172,16 +66847,20 @@
       <c r="AH150">
         <v>1200</v>
       </c>
-    </row>
-    <row r="151" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>249</v>
+      <c r="AI150" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="151" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A151" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B151" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C151" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C151" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 904,02HP 3617,85762711864V 136,08064516129AMP</v>
       </c>
       <c r="D151">
         <v>31.1</v>
@@ -66276,16 +66955,20 @@
       <c r="AH151">
         <v>1200</v>
       </c>
-    </row>
-    <row r="152" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>249</v>
+      <c r="AI151" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="152" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A152" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B152" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C152" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C152" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 951,6HP 3808,27118644068V 136,08064516129AMP</v>
       </c>
       <c r="D152">
         <v>32.6</v>
@@ -66380,16 +67063,20 @@
       <c r="AH152">
         <v>1200</v>
       </c>
-    </row>
-    <row r="153" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>249</v>
+      <c r="AI152" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="153" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A153" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B153" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C153" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C153" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 1000HP 3998,68474576271V 136,08064516129AMP</v>
       </c>
       <c r="D153">
         <v>34.1</v>
@@ -66484,16 +67171,20 @@
       <c r="AH153">
         <v>1200</v>
       </c>
-    </row>
-    <row r="154" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>249</v>
+      <c r="AI153" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="154" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A154" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B154" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C154" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C154" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 256HP 3520V 31AMP</v>
       </c>
       <c r="D154">
         <v>13.5</v>
@@ -66588,16 +67279,20 @@
       <c r="AH154">
         <v>1200</v>
       </c>
-    </row>
-    <row r="155" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>249</v>
+      <c r="AI154" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="155" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A155" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B155" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C155" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C155" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 238HP 3778V 34,3AMP</v>
       </c>
       <c r="D155">
         <v>13.5</v>
@@ -66692,16 +67387,20 @@
       <c r="AH155">
         <v>1200</v>
       </c>
-    </row>
-    <row r="156" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>249</v>
+      <c r="AI155" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="156" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A156" s="14" t="s">
+        <v>523</v>
       </c>
       <c r="B156" s="114" t="s">
-        <v>379</v>
-      </c>
-      <c r="C156" s="107" t="s">
-        <v>380</v>
+        <v>378</v>
+      </c>
+      <c r="C156" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>SPECTRUM PMM 333,06HP 3569V 50,3AMP</v>
       </c>
       <c r="D156">
         <v>13.5</v>
@@ -66796,8 +67495,11 @@
       <c r="AH156">
         <v>1200</v>
       </c>
-    </row>
-    <row r="157" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI156" s="107" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="157" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>59</v>
       </c>
@@ -66805,7 +67507,7 @@
         <v>460</v>
       </c>
       <c r="C157" s="107" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D157">
         <v>8.1</v>
@@ -66898,7 +67600,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="158" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>59</v>
       </c>
@@ -66906,7 +67608,7 @@
         <v>460</v>
       </c>
       <c r="C158" s="107" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D158">
         <v>9.5</v>
@@ -66999,7 +67701,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="159" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>59</v>
       </c>
@@ -67007,7 +67709,7 @@
         <v>460</v>
       </c>
       <c r="C159" s="107" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D159">
         <v>10.8</v>
@@ -67100,7 +67802,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="160" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>59</v>
       </c>
@@ -67108,7 +67810,7 @@
         <v>460</v>
       </c>
       <c r="C160" s="107" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D160">
         <v>12.2</v>
@@ -67209,7 +67911,7 @@
         <v>460</v>
       </c>
       <c r="C161" s="107" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D161">
         <v>14.9</v>
@@ -67310,7 +68012,7 @@
         <v>460</v>
       </c>
       <c r="C162" s="107" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D162">
         <v>19</v>
@@ -67411,7 +68113,7 @@
         <v>460</v>
       </c>
       <c r="C163" s="107" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D163">
         <v>20.3</v>
@@ -67512,7 +68214,7 @@
         <v>460</v>
       </c>
       <c r="C164" s="107" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D164">
         <v>21.7</v>
@@ -67613,7 +68315,7 @@
         <v>460</v>
       </c>
       <c r="C165" s="107" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D165">
         <v>23</v>
@@ -67714,7 +68416,7 @@
         <v>512</v>
       </c>
       <c r="C166" s="107" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D166">
         <v>8.3000000000000007</v>
@@ -67815,7 +68517,7 @@
         <v>512</v>
       </c>
       <c r="C167" s="107" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D167">
         <v>13.8</v>
@@ -67916,7 +68618,7 @@
         <v>512</v>
       </c>
       <c r="C168" s="107" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D168">
         <v>17.899999999999999</v>
@@ -68017,7 +68719,7 @@
         <v>512</v>
       </c>
       <c r="C169" s="107" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D169">
         <v>19.3</v>
@@ -68118,7 +68820,7 @@
         <v>512</v>
       </c>
       <c r="C170" s="107" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D170">
         <v>22</v>
@@ -68219,7 +68921,7 @@
         <v>512</v>
       </c>
       <c r="C171" s="107" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D171">
         <v>23.4</v>
@@ -68320,7 +69022,7 @@
         <v>512</v>
       </c>
       <c r="C172" s="107" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D172">
         <v>26.1</v>
@@ -68421,7 +69123,7 @@
         <v>512</v>
       </c>
       <c r="C173" s="107" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D173">
         <v>27.5</v>
@@ -68522,7 +69224,7 @@
         <v>512</v>
       </c>
       <c r="C174" s="107" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D174">
         <v>49</v>
@@ -68623,7 +69325,7 @@
         <v>406</v>
       </c>
       <c r="C175" s="107" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D175">
         <v>14.7</v>
@@ -68724,7 +69426,7 @@
         <v>406</v>
       </c>
       <c r="C176" s="107" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D176">
         <v>17</v>
@@ -68825,7 +69527,7 @@
         <v>406</v>
       </c>
       <c r="C177" s="107" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D177">
         <v>20.399999999999999</v>
@@ -68926,7 +69628,7 @@
         <v>406</v>
       </c>
       <c r="C178" s="107" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D178">
         <v>23.8</v>
@@ -69027,7 +69729,7 @@
         <v>406</v>
       </c>
       <c r="C179" s="107" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D179">
         <v>45.3</v>
@@ -69128,7 +69830,7 @@
         <v>460</v>
       </c>
       <c r="C180" s="107" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D180">
         <v>12.5</v>
@@ -69229,7 +69931,7 @@
         <v>460</v>
       </c>
       <c r="C181" s="107" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D181">
         <v>13.8</v>
@@ -69330,7 +70032,7 @@
         <v>460</v>
       </c>
       <c r="C182" s="107" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D182">
         <v>16.100000000000001</v>
@@ -69431,7 +70133,7 @@
         <v>460</v>
       </c>
       <c r="C183" s="107" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D183">
         <v>20</v>
@@ -69532,7 +70234,7 @@
         <v>460</v>
       </c>
       <c r="C184" s="107" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D184">
         <v>22.3</v>
@@ -69633,7 +70335,7 @@
         <v>460</v>
       </c>
       <c r="C185" s="107" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D185">
         <v>28.7</v>
@@ -69734,7 +70436,7 @@
         <v>460</v>
       </c>
       <c r="C186" s="107" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D186">
         <v>44.6</v>
@@ -69835,7 +70537,7 @@
         <v>512</v>
       </c>
       <c r="C187" s="107" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D187">
         <v>14.1</v>
@@ -69936,7 +70638,7 @@
         <v>512</v>
       </c>
       <c r="C188" s="107" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D188">
         <v>50.8</v>
@@ -70037,7 +70739,7 @@
         <v>512</v>
       </c>
       <c r="C189" s="107" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D189">
         <v>80.900000000000006</v>
@@ -70138,7 +70840,7 @@
         <v>562</v>
       </c>
       <c r="C190" s="107" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D190">
         <v>10.5</v>
@@ -70239,7 +70941,7 @@
         <v>562</v>
       </c>
       <c r="C191" s="107" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D191">
         <v>17.899999999999999</v>
@@ -70340,7 +71042,7 @@
         <v>562</v>
       </c>
       <c r="C192" s="107" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D192">
         <v>23.8</v>
@@ -70441,7 +71143,7 @@
         <v>562</v>
       </c>
       <c r="C193" s="107" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D193">
         <v>19.3</v>
@@ -70542,7 +71244,7 @@
         <v>562</v>
       </c>
       <c r="C194" s="107" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D194">
         <v>25.2</v>
@@ -70643,7 +71345,7 @@
         <v>562</v>
       </c>
       <c r="C195" s="107" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D195">
         <v>26.7</v>
@@ -70744,7 +71446,7 @@
         <v>562</v>
       </c>
       <c r="C196" s="107" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D196">
         <v>35.200000000000003</v>
@@ -70845,7 +71547,7 @@
         <v>562</v>
       </c>
       <c r="C197" s="107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D197">
         <v>38.200000000000003</v>
@@ -70946,7 +71648,7 @@
         <v>562</v>
       </c>
       <c r="C198" s="107" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D198">
         <v>41.2</v>
@@ -71047,7 +71749,7 @@
         <v>562</v>
       </c>
       <c r="C199" s="107" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D199">
         <v>50</v>
@@ -71148,7 +71850,7 @@
         <v>562</v>
       </c>
       <c r="C200" s="107" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D200">
         <v>70.3</v>
@@ -71243,13 +71945,13 @@
     </row>
     <row r="201" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B201" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C201" t="s">
-        <v>426</v>
+        <v>524</v>
       </c>
       <c r="D201">
         <v>25.7</v>
@@ -71347,13 +72049,13 @@
     </row>
     <row r="202" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B202" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C202" t="s">
-        <v>426</v>
+        <v>525</v>
       </c>
       <c r="D202">
         <v>25.7</v>
@@ -71451,13 +72153,13 @@
     </row>
     <row r="203" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B203" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C203" t="s">
-        <v>426</v>
+        <v>526</v>
       </c>
       <c r="D203">
         <v>34</v>
@@ -71555,13 +72257,13 @@
     </row>
     <row r="204" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B204" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C204" t="s">
-        <v>426</v>
+        <v>527</v>
       </c>
       <c r="D204">
         <v>34</v>
@@ -71659,13 +72361,13 @@
     </row>
     <row r="205" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B205" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C205" t="s">
-        <v>426</v>
+        <v>528</v>
       </c>
       <c r="D205">
         <v>34</v>
@@ -71763,13 +72465,13 @@
     </row>
     <row r="206" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B206" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C206" t="s">
-        <v>426</v>
+        <v>529</v>
       </c>
       <c r="D206">
         <v>18</v>
@@ -71867,13 +72569,13 @@
     </row>
     <row r="207" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B207" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C207" t="s">
-        <v>426</v>
+        <v>530</v>
       </c>
       <c r="D207">
         <v>34</v>
@@ -71971,13 +72673,13 @@
     </row>
     <row r="208" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B208" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C208" t="s">
-        <v>426</v>
+        <v>531</v>
       </c>
       <c r="D208">
         <v>68</v>
@@ -72075,13 +72777,13 @@
     </row>
     <row r="209" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B209" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C209" t="s">
-        <v>426</v>
+        <v>532</v>
       </c>
       <c r="D209">
         <v>68</v>
@@ -72179,13 +72881,13 @@
     </row>
     <row r="210" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B210" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C210" t="s">
-        <v>426</v>
+        <v>533</v>
       </c>
       <c r="D210">
         <v>34</v>
@@ -72283,13 +72985,13 @@
     </row>
     <row r="211" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B211" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C211" t="s">
-        <v>426</v>
+        <v>534</v>
       </c>
       <c r="D211">
         <v>68</v>
@@ -72387,13 +73089,13 @@
     </row>
     <row r="212" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B212" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C212" t="s">
-        <v>426</v>
+        <v>535</v>
       </c>
       <c r="D212">
         <v>25.7</v>
@@ -72491,13 +73193,13 @@
     </row>
     <row r="213" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B213" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C213" t="s">
-        <v>426</v>
+        <v>536</v>
       </c>
       <c r="D213">
         <v>34</v>
@@ -72595,13 +73297,13 @@
     </row>
     <row r="214" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B214" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C214" t="s">
-        <v>426</v>
+        <v>537</v>
       </c>
       <c r="D214">
         <v>34</v>
@@ -72699,13 +73401,13 @@
     </row>
     <row r="215" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B215" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C215" t="s">
-        <v>426</v>
+        <v>534</v>
       </c>
       <c r="D215">
         <v>68</v>
@@ -72803,13 +73505,13 @@
     </row>
     <row r="216" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B216" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C216" t="s">
-        <v>426</v>
+        <v>538</v>
       </c>
       <c r="D216">
         <v>68</v>
@@ -72907,13 +73609,13 @@
     </row>
     <row r="217" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B217" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C217" t="s">
-        <v>426</v>
+        <v>531</v>
       </c>
       <c r="D217">
         <v>68</v>
@@ -73011,13 +73713,13 @@
     </row>
     <row r="218" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
+        <v>424</v>
+      </c>
+      <c r="B218" s="114" t="s">
         <v>425</v>
       </c>
-      <c r="B218" s="114" t="s">
-        <v>427</v>
-      </c>
       <c r="C218" t="s">
-        <v>426</v>
+        <v>539</v>
       </c>
       <c r="D218">
         <v>31</v>
@@ -73115,13 +73817,13 @@
     </row>
     <row r="219" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
+        <v>424</v>
+      </c>
+      <c r="B219" s="114" t="s">
         <v>425</v>
       </c>
-      <c r="B219" s="114" t="s">
-        <v>427</v>
-      </c>
       <c r="C219" t="s">
-        <v>426</v>
+        <v>540</v>
       </c>
       <c r="D219">
         <v>31</v>
@@ -73219,13 +73921,13 @@
     </row>
     <row r="220" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
+        <v>424</v>
+      </c>
+      <c r="B220" s="114" t="s">
         <v>425</v>
       </c>
-      <c r="B220" s="114" t="s">
-        <v>427</v>
-      </c>
       <c r="C220" t="s">
-        <v>426</v>
+        <v>541</v>
       </c>
       <c r="D220">
         <v>31</v>
@@ -73323,13 +74025,13 @@
     </row>
     <row r="221" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
+        <v>424</v>
+      </c>
+      <c r="B221" s="114" t="s">
         <v>425</v>
       </c>
-      <c r="B221" s="114" t="s">
-        <v>427</v>
-      </c>
       <c r="C221" t="s">
-        <v>426</v>
+        <v>542</v>
       </c>
       <c r="D221">
         <v>31</v>
@@ -73427,13 +74129,13 @@
     </row>
     <row r="222" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
+        <v>424</v>
+      </c>
+      <c r="B222" s="114" t="s">
         <v>425</v>
       </c>
-      <c r="B222" s="114" t="s">
-        <v>427</v>
-      </c>
       <c r="C222" t="s">
-        <v>426</v>
+        <v>543</v>
       </c>
       <c r="D222">
         <v>31</v>
@@ -73531,13 +74233,13 @@
     </row>
     <row r="223" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B223" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C223" t="s">
-        <v>426</v>
+        <v>544</v>
       </c>
       <c r="D223">
         <v>34</v>
@@ -73635,13 +74337,13 @@
     </row>
     <row r="224" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B224" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C224" t="s">
-        <v>426</v>
+        <v>545</v>
       </c>
       <c r="D224">
         <v>34</v>
@@ -73739,13 +74441,13 @@
     </row>
     <row r="225" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B225" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C225" t="s">
-        <v>426</v>
+        <v>546</v>
       </c>
       <c r="D225">
         <v>34</v>
@@ -73843,13 +74545,13 @@
     </row>
     <row r="226" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B226" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C226" t="s">
-        <v>426</v>
+        <v>547</v>
       </c>
       <c r="D226">
         <v>34</v>
@@ -73947,13 +74649,13 @@
     </row>
     <row r="227" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B227" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C227" t="s">
-        <v>426</v>
+        <v>548</v>
       </c>
       <c r="D227">
         <v>25.7</v>
@@ -74051,13 +74753,13 @@
     </row>
     <row r="228" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B228" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C228" t="s">
-        <v>426</v>
+        <v>549</v>
       </c>
       <c r="D228">
         <v>25.7</v>
@@ -74155,13 +74857,13 @@
     </row>
     <row r="229" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B229" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C229" t="s">
-        <v>426</v>
+        <v>550</v>
       </c>
       <c r="D229">
         <v>25.7</v>
@@ -74259,13 +74961,13 @@
     </row>
     <row r="230" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B230" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C230" t="s">
-        <v>428</v>
+        <v>551</v>
       </c>
       <c r="D230">
         <v>25.7</v>
@@ -74363,13 +75065,13 @@
     </row>
     <row r="231" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
+        <v>424</v>
+      </c>
+      <c r="B231" s="114" t="s">
         <v>425</v>
       </c>
-      <c r="B231" s="114" t="s">
-        <v>427</v>
-      </c>
       <c r="C231" t="s">
-        <v>429</v>
+        <v>552</v>
       </c>
       <c r="D231">
         <v>31</v>
@@ -74467,13 +75169,13 @@
     </row>
     <row r="232" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B232" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C232" t="s">
-        <v>426</v>
+        <v>553</v>
       </c>
       <c r="D232">
         <v>34</v>
@@ -74571,13 +75273,13 @@
     </row>
     <row r="233" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B233" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C233" t="s">
-        <v>429</v>
+        <v>554</v>
       </c>
       <c r="D233">
         <v>68</v>
@@ -74675,13 +75377,13 @@
     </row>
     <row r="234" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B234" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C234" t="s">
-        <v>426</v>
+        <v>555</v>
       </c>
       <c r="D234">
         <v>68</v>
@@ -74779,13 +75481,13 @@
     </row>
     <row r="235" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B235" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C235" t="s">
-        <v>426</v>
+        <v>556</v>
       </c>
       <c r="D235">
         <v>68</v>
@@ -74883,13 +75585,13 @@
     </row>
     <row r="236" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B236" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C236" t="s">
-        <v>426</v>
+        <v>557</v>
       </c>
       <c r="D236">
         <v>68</v>
@@ -74987,13 +75689,13 @@
     </row>
     <row r="237" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B237" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C237" t="s">
-        <v>426</v>
+        <v>547</v>
       </c>
       <c r="D237">
         <v>68</v>
@@ -75091,13 +75793,13 @@
     </row>
     <row r="238" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B238" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C238" t="s">
-        <v>426</v>
+        <v>558</v>
       </c>
       <c r="D238">
         <v>68</v>
@@ -75195,13 +75897,13 @@
     </row>
     <row r="239" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B239" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C239" t="s">
-        <v>426</v>
+        <v>559</v>
       </c>
       <c r="D239">
         <v>68</v>
@@ -75299,13 +76001,13 @@
     </row>
     <row r="240" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B240" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C240" t="s">
-        <v>426</v>
+        <v>560</v>
       </c>
       <c r="D240">
         <v>25.7</v>
@@ -75403,13 +76105,13 @@
     </row>
     <row r="241" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B241" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C241" t="s">
-        <v>426</v>
+        <v>561</v>
       </c>
       <c r="D241">
         <v>25.7</v>
@@ -75507,13 +76209,13 @@
     </row>
     <row r="242" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B242" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C242" t="s">
-        <v>426</v>
+        <v>562</v>
       </c>
       <c r="D242">
         <v>25.7</v>
@@ -75611,13 +76313,13 @@
     </row>
     <row r="243" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B243" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C243" t="s">
-        <v>430</v>
+        <v>563</v>
       </c>
       <c r="D243">
         <v>68</v>
@@ -75715,13 +76417,13 @@
     </row>
     <row r="244" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B244" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C244" t="s">
-        <v>430</v>
+        <v>564</v>
       </c>
       <c r="D244">
         <v>68</v>
@@ -75819,13 +76521,13 @@
     </row>
     <row r="245" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B245" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C245" t="s">
-        <v>430</v>
+        <v>565</v>
       </c>
       <c r="D245">
         <v>68</v>
@@ -75923,13 +76625,13 @@
     </row>
     <row r="246" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B246" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C246" t="s">
-        <v>426</v>
+        <v>566</v>
       </c>
       <c r="D246">
         <v>68</v>
@@ -76027,13 +76729,13 @@
     </row>
     <row r="247" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B247" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C247" t="s">
-        <v>426</v>
+        <v>567</v>
       </c>
       <c r="D247">
         <v>25.7</v>
@@ -76131,13 +76833,13 @@
     </row>
     <row r="248" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B248" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C248" t="s">
-        <v>426</v>
+        <v>534</v>
       </c>
       <c r="D248">
         <v>68</v>
@@ -76235,13 +76937,13 @@
     </row>
     <row r="249" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B249" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C249" t="s">
-        <v>429</v>
+        <v>568</v>
       </c>
       <c r="D249">
         <v>68</v>
@@ -76339,13 +77041,13 @@
     </row>
     <row r="250" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B250" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C250" t="s">
-        <v>430</v>
+        <v>569</v>
       </c>
       <c r="D250">
         <v>68</v>
@@ -76443,13 +77145,13 @@
     </row>
     <row r="251" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
+        <v>424</v>
+      </c>
+      <c r="B251" s="114" t="s">
         <v>425</v>
       </c>
-      <c r="B251" s="114" t="s">
-        <v>427</v>
-      </c>
       <c r="C251" t="s">
-        <v>430</v>
+        <v>570</v>
       </c>
       <c r="D251">
         <v>31</v>
@@ -76547,13 +77249,13 @@
     </row>
     <row r="252" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
+        <v>424</v>
+      </c>
+      <c r="B252" s="114" t="s">
         <v>425</v>
       </c>
-      <c r="B252" s="114" t="s">
-        <v>427</v>
-      </c>
       <c r="C252" t="s">
-        <v>430</v>
+        <v>571</v>
       </c>
       <c r="D252">
         <v>31</v>
@@ -76651,13 +77353,13 @@
     </row>
     <row r="253" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B253" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C253" t="s">
-        <v>429</v>
+        <v>572</v>
       </c>
       <c r="D253">
         <v>100</v>
@@ -76755,13 +77457,13 @@
     </row>
     <row r="254" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B254" s="114" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C254" t="s">
-        <v>432</v>
+        <v>573</v>
       </c>
       <c r="D254">
         <v>25</v>
@@ -76859,13 +77561,13 @@
     </row>
     <row r="255" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B255" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C255" t="s">
-        <v>433</v>
+        <v>574</v>
       </c>
       <c r="D255">
         <v>30</v>
@@ -76963,13 +77665,13 @@
     </row>
     <row r="256" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B256" s="114" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C256" t="s">
-        <v>432</v>
+        <v>575</v>
       </c>
       <c r="D256">
         <v>25</v>
@@ -77067,13 +77769,13 @@
     </row>
     <row r="257" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B257" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C257" t="s">
-        <v>433</v>
+        <v>576</v>
       </c>
       <c r="D257">
         <v>30</v>
@@ -77171,13 +77873,13 @@
     </row>
     <row r="258" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B258" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C258" t="s">
-        <v>433</v>
+        <v>577</v>
       </c>
       <c r="D258">
         <v>30</v>
@@ -77275,13 +77977,13 @@
     </row>
     <row r="259" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B259" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C259" t="s">
-        <v>433</v>
+        <v>578</v>
       </c>
       <c r="D259">
         <v>30</v>
@@ -77379,13 +78081,13 @@
     </row>
     <row r="260" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B260" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C260" t="s">
-        <v>426</v>
+        <v>579</v>
       </c>
       <c r="D260">
         <v>34</v>
@@ -77483,13 +78185,13 @@
     </row>
     <row r="261" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B261" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C261" t="s">
-        <v>426</v>
+        <v>538</v>
       </c>
       <c r="D261">
         <v>68</v>
@@ -77587,13 +78289,13 @@
     </row>
     <row r="262" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
+        <v>424</v>
+      </c>
+      <c r="B262" s="114" t="s">
         <v>425</v>
       </c>
-      <c r="B262" s="114" t="s">
-        <v>427</v>
-      </c>
       <c r="C262" t="s">
-        <v>430</v>
+        <v>580</v>
       </c>
       <c r="D262">
         <v>61.5</v>
@@ -77691,13 +78393,13 @@
     </row>
     <row r="263" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B263" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C263" t="s">
-        <v>434</v>
+        <v>581</v>
       </c>
       <c r="D263">
         <v>3.8</v>
@@ -77795,13 +78497,13 @@
     </row>
     <row r="264" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B264" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C264" t="s">
-        <v>435</v>
+        <v>582</v>
       </c>
       <c r="D264">
         <v>3.8</v>
@@ -77899,13 +78601,13 @@
     </row>
     <row r="265" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B265" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C265" t="s">
-        <v>434</v>
+        <v>583</v>
       </c>
       <c r="D265">
         <v>5.0999999999999996</v>
@@ -78003,13 +78705,13 @@
     </row>
     <row r="266" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B266" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C266" t="s">
-        <v>435</v>
+        <v>584</v>
       </c>
       <c r="D266">
         <v>5.0999999999999996</v>
@@ -78107,13 +78809,13 @@
     </row>
     <row r="267" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B267" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C267" t="s">
-        <v>434</v>
+        <v>585</v>
       </c>
       <c r="D267">
         <v>6.3451443569553803</v>
@@ -78211,13 +78913,13 @@
     </row>
     <row r="268" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B268" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C268" t="s">
-        <v>435</v>
+        <v>586</v>
       </c>
       <c r="D268">
         <v>6.3451443569553803</v>
@@ -78315,13 +79017,13 @@
     </row>
     <row r="269" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B269" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C269" t="s">
-        <v>434</v>
+        <v>587</v>
       </c>
       <c r="D269">
         <v>7.591863517060367</v>
@@ -78419,13 +79121,13 @@
     </row>
     <row r="270" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B270" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C270" t="s">
-        <v>435</v>
+        <v>588</v>
       </c>
       <c r="D270">
         <v>7.591863517060367</v>
@@ -78523,13 +79225,13 @@
     </row>
     <row r="271" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B271" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C271" t="s">
-        <v>434</v>
+        <v>589</v>
       </c>
       <c r="D271">
         <v>8.8385826771653537</v>
@@ -78627,13 +79329,13 @@
     </row>
     <row r="272" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B272" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C272" t="s">
-        <v>435</v>
+        <v>590</v>
       </c>
       <c r="D272">
         <v>8.8385826771653537</v>
@@ -78731,13 +79433,13 @@
     </row>
     <row r="273" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B273" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C273" t="s">
-        <v>434</v>
+        <v>591</v>
       </c>
       <c r="D273">
         <v>10.08530183727034</v>
@@ -78835,13 +79537,13 @@
     </row>
     <row r="274" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B274" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C274" t="s">
-        <v>435</v>
+        <v>592</v>
       </c>
       <c r="D274">
         <v>10.08530183727034</v>
@@ -78939,13 +79641,13 @@
     </row>
     <row r="275" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B275" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C275" t="s">
-        <v>434</v>
+        <v>593</v>
       </c>
       <c r="D275">
         <v>11.332020997375329</v>
@@ -79043,13 +79745,13 @@
     </row>
     <row r="276" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B276" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C276" t="s">
-        <v>435</v>
+        <v>594</v>
       </c>
       <c r="D276">
         <v>11.332020997375329</v>
@@ -79147,13 +79849,13 @@
     </row>
     <row r="277" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B277" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C277" t="s">
-        <v>434</v>
+        <v>595</v>
       </c>
       <c r="D277">
         <v>12.578740157480315</v>
@@ -79251,13 +79953,13 @@
     </row>
     <row r="278" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B278" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C278" t="s">
-        <v>435</v>
+        <v>596</v>
       </c>
       <c r="D278">
         <v>12.578740157480315</v>
@@ -79355,13 +80057,13 @@
     </row>
     <row r="279" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B279" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C279" t="s">
-        <v>434</v>
+        <v>597</v>
       </c>
       <c r="D279">
         <v>13.825459317585302</v>
@@ -79459,13 +80161,13 @@
     </row>
     <row r="280" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B280" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C280" t="s">
-        <v>435</v>
+        <v>598</v>
       </c>
       <c r="D280">
         <v>13.825459317585302</v>
@@ -79563,13 +80265,13 @@
     </row>
     <row r="281" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B281" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C281" t="s">
-        <v>434</v>
+        <v>599</v>
       </c>
       <c r="D281">
         <v>15.072178477690288</v>
@@ -79667,13 +80369,13 @@
     </row>
     <row r="282" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B282" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C282" t="s">
-        <v>435</v>
+        <v>600</v>
       </c>
       <c r="D282">
         <v>15.072178477690288</v>
@@ -79771,13 +80473,13 @@
     </row>
     <row r="283" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B283" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C283" t="s">
-        <v>434</v>
+        <v>601</v>
       </c>
       <c r="D283">
         <v>16.318897637795274</v>
@@ -79875,13 +80577,13 @@
     </row>
     <row r="284" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B284" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C284" t="s">
-        <v>435</v>
+        <v>602</v>
       </c>
       <c r="D284">
         <v>16.318897637795274</v>
@@ -79979,13 +80681,13 @@
     </row>
     <row r="285" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B285" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C285" t="s">
-        <v>436</v>
+        <v>603</v>
       </c>
       <c r="D285">
         <v>17.565616797900262</v>
@@ -80083,13 +80785,13 @@
     </row>
     <row r="286" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B286" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C286" t="s">
-        <v>436</v>
+        <v>604</v>
       </c>
       <c r="D286">
         <v>18.812335958005249</v>
@@ -80187,13 +80889,13 @@
     </row>
     <row r="287" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B287" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C287" t="s">
-        <v>434</v>
+        <v>605</v>
       </c>
       <c r="D287">
         <v>20.059055118110233</v>
@@ -80291,13 +80993,13 @@
     </row>
     <row r="288" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B288" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C288" t="s">
-        <v>435</v>
+        <v>606</v>
       </c>
       <c r="D288">
         <v>20.059055118110233</v>
@@ -80395,13 +81097,13 @@
     </row>
     <row r="289" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B289" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C289" t="s">
-        <v>436</v>
+        <v>607</v>
       </c>
       <c r="D289">
         <v>22.552493438320209</v>
@@ -80499,13 +81201,13 @@
     </row>
     <row r="290" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B290" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C290" t="s">
-        <v>436</v>
+        <v>608</v>
       </c>
       <c r="D290">
         <v>25.045931758530184</v>
@@ -80603,13 +81305,13 @@
     </row>
     <row r="291" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B291" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C291" t="s">
-        <v>436</v>
+        <v>609</v>
       </c>
       <c r="D291">
         <v>22.6</v>
@@ -80707,13 +81409,13 @@
     </row>
     <row r="292" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B292" s="114" t="s">
         <v>213</v>
       </c>
       <c r="C292" t="s">
-        <v>436</v>
+        <v>610</v>
       </c>
       <c r="D292">
         <v>24.9</v>
@@ -80811,13 +81513,13 @@
     </row>
     <row r="293" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B293" s="114" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C293" t="s">
-        <v>437</v>
+        <v>611</v>
       </c>
       <c r="D293">
         <v>102</v>
@@ -80914,7 +81616,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AH200" xr:uid="{E430685C-2EB8-41AB-A6F6-39B25D30911C}"/>
+  <autoFilter ref="A3:AH293" xr:uid="{E430685C-2EB8-41AB-A6F6-39B25D30911C}"/>
   <mergeCells count="6">
     <mergeCell ref="AF1:AJ1"/>
     <mergeCell ref="A1:G1"/>
